--- a/results/ref_threshold_sensitivity/tables/threshold_comparison_summary.xlsx
+++ b/results/ref_threshold_sensitivity/tables/threshold_comparison_summary.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -496,25 +496,25 @@
         <v>11</v>
       </c>
       <c r="E2" t="n">
-        <v>0.5755852889762156</v>
+        <v>0.5755852889762161</v>
       </c>
       <c r="F2" t="n">
-        <v>0.1511705779524313</v>
+        <v>0.1511705779524322</v>
       </c>
       <c r="G2" t="n">
-        <v>1.356185999273622</v>
+        <v>1.356185999273623</v>
       </c>
       <c r="H2" t="n">
         <v>0.199</v>
       </c>
       <c r="I2" t="n">
-        <v>190.693409899824</v>
+        <v>190.6934098998242</v>
       </c>
       <c r="J2" t="n">
         <v>331.3034810861955</v>
       </c>
       <c r="K2" t="n">
-        <v>8.294327430324548</v>
+        <v>8.294327430324556</v>
       </c>
     </row>
     <row r="3">
@@ -533,10 +533,10 @@
         <v>16</v>
       </c>
       <c r="E3" t="n">
-        <v>0.5256219687263332</v>
+        <v>0.5256219687263333</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2884329530894998</v>
+        <v>0.2884329530894999</v>
       </c>
       <c r="G3" t="n">
         <v>2.216046840597066</v>
@@ -570,25 +570,25 @@
         <v>20</v>
       </c>
       <c r="E4" t="n">
-        <v>0.4240549598658212</v>
+        <v>0.4240549598658218</v>
       </c>
       <c r="F4" t="n">
-        <v>0.218360302675043</v>
+        <v>0.2183603026750438</v>
       </c>
       <c r="G4" t="n">
-        <v>2.061574985258455</v>
+        <v>2.061574985258458</v>
       </c>
       <c r="H4" t="n">
         <v>0.004</v>
       </c>
       <c r="I4" t="n">
-        <v>262.0799181803195</v>
+        <v>262.0799181803198</v>
       </c>
       <c r="J4" t="n">
         <v>618.0329037142883</v>
       </c>
       <c r="K4" t="n">
-        <v>8.532316708043737</v>
+        <v>8.532316708043751</v>
       </c>
     </row>
     <row r="5">
@@ -607,10 +607,10 @@
         <v>25</v>
       </c>
       <c r="E5" t="n">
-        <v>0.3430968682153295</v>
+        <v>0.3430968682153296</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1702276230088373</v>
+        <v>0.1702276230088375</v>
       </c>
       <c r="G5" t="n">
         <v>1.98471895799337</v>
@@ -619,13 +619,13 @@
         <v>0.01</v>
       </c>
       <c r="I5" t="n">
-        <v>248.3873571825596</v>
+        <v>248.3873571825597</v>
       </c>
       <c r="J5" t="n">
         <v>723.9569351786397</v>
       </c>
       <c r="K5" t="n">
-        <v>6.183664494146679</v>
+        <v>6.183664494146682</v>
       </c>
     </row>
     <row r="6">
@@ -644,25 +644,25 @@
         <v>30</v>
       </c>
       <c r="E6" t="n">
-        <v>0.3405615461937536</v>
+        <v>0.3405615461937538</v>
       </c>
       <c r="F6" t="n">
-        <v>0.2031785349841191</v>
+        <v>0.2031785349841192</v>
       </c>
       <c r="G6" t="n">
-        <v>2.478920378838444</v>
+        <v>2.478920378838445</v>
       </c>
       <c r="H6" t="n">
         <v>0.001</v>
       </c>
       <c r="I6" t="n">
-        <v>311.3986155603584</v>
+        <v>311.3986155603586</v>
       </c>
       <c r="J6" t="n">
         <v>914.3681047982918</v>
       </c>
       <c r="K6" t="n">
-        <v>7.388694435646968</v>
+        <v>7.388694435646975</v>
       </c>
     </row>
     <row r="7">
@@ -681,25 +681,25 @@
         <v>34</v>
       </c>
       <c r="E7" t="n">
-        <v>0.2817620862995143</v>
+        <v>0.2817620862995145</v>
       </c>
       <c r="F7" t="n">
-        <v>0.153505315995856</v>
+        <v>0.1535053159958564</v>
       </c>
       <c r="G7" t="n">
-        <v>2.196859359801592</v>
+        <v>2.196859359801594</v>
       </c>
       <c r="H7" t="n">
         <v>0.001</v>
       </c>
       <c r="I7" t="n">
-        <v>290.341761622797</v>
+        <v>290.3417616227973</v>
       </c>
       <c r="J7" t="n">
         <v>1030.450070255948</v>
       </c>
       <c r="K7" t="n">
-        <v>5.828707214872588</v>
+        <v>5.828707214872598</v>
       </c>
     </row>
     <row r="8">
@@ -718,25 +718,25 @@
         <v>39</v>
       </c>
       <c r="E8" t="n">
-        <v>0.2551292489076616</v>
+        <v>0.2551292489076619</v>
       </c>
       <c r="F8" t="n">
-        <v>0.1422700441967012</v>
+        <v>0.1422700441967016</v>
       </c>
       <c r="G8" t="n">
-        <v>2.260597614178338</v>
+        <v>2.260597614178341</v>
       </c>
       <c r="H8" t="n">
         <v>0.001</v>
       </c>
       <c r="I8" t="n">
-        <v>296.5920555245091</v>
+        <v>296.5920555245094</v>
       </c>
       <c r="J8" t="n">
         <v>1162.51686858473</v>
       </c>
       <c r="K8" t="n">
-        <v>5.705509415246405</v>
+        <v>5.705509415246414</v>
       </c>
     </row>
     <row r="9">
@@ -755,25 +755,25 @@
         <v>44</v>
       </c>
       <c r="E9" t="n">
-        <v>0.2600434908304278</v>
+        <v>0.2600434908304277</v>
       </c>
       <c r="F9" t="n">
-        <v>0.162680792255484</v>
+        <v>0.1626807922554839</v>
       </c>
       <c r="G9" t="n">
-        <v>2.670873903831482</v>
+        <v>2.670873903831481</v>
       </c>
       <c r="H9" t="n">
         <v>0.001</v>
       </c>
       <c r="I9" t="n">
-        <v>340.597427048197</v>
+        <v>340.5974270481969</v>
       </c>
       <c r="J9" t="n">
         <v>1309.77101545794</v>
       </c>
       <c r="K9" t="n">
-        <v>6.079869406982931</v>
+        <v>6.079869406982926</v>
       </c>
     </row>
     <row r="10">
@@ -792,25 +792,25 @@
         <v>48</v>
       </c>
       <c r="E10" t="n">
-        <v>0.2958595079622765</v>
+        <v>0.2958595079622763</v>
       </c>
       <c r="F10" t="n">
-        <v>0.2120332589101666</v>
+        <v>0.2120332589101663</v>
       </c>
       <c r="G10" t="n">
-        <v>3.529437512805299</v>
+        <v>3.529437512805296</v>
       </c>
       <c r="H10" t="n">
         <v>0.001</v>
       </c>
       <c r="I10" t="n">
-        <v>436.2145161079195</v>
+        <v>436.2145161079192</v>
       </c>
       <c r="J10" t="n">
         <v>1474.397490593876</v>
       </c>
       <c r="K10" t="n">
-        <v>7.515089085891463</v>
+        <v>7.515089085891455</v>
       </c>
     </row>
     <row r="11">
@@ -829,25 +829,25 @@
         <v>53</v>
       </c>
       <c r="E11" t="n">
-        <v>0.2860611958570174</v>
+        <v>0.286061195857017</v>
       </c>
       <c r="F11" t="n">
-        <v>0.2101102592460617</v>
+        <v>0.2101102592460613</v>
       </c>
       <c r="G11" t="n">
-        <v>3.766394578151316</v>
+        <v>3.766394578151311</v>
       </c>
       <c r="H11" t="n">
         <v>0.001</v>
       </c>
       <c r="I11" t="n">
-        <v>448.2318414853752</v>
+        <v>448.2318414853746</v>
       </c>
       <c r="J11" t="n">
         <v>1566.908927100395</v>
       </c>
       <c r="K11" t="n">
-        <v>7.188244463959993</v>
+        <v>7.188244463959986</v>
       </c>
     </row>
     <row r="12">
@@ -866,25 +866,25 @@
         <v>58</v>
       </c>
       <c r="E12" t="n">
-        <v>0.2893160670625267</v>
+        <v>0.2893160670625263</v>
       </c>
       <c r="F12" t="n">
-        <v>0.2209810735108466</v>
+        <v>0.2209810735108461</v>
       </c>
       <c r="G12" t="n">
-        <v>4.233790800663849</v>
+        <v>4.233790800663843</v>
       </c>
       <c r="H12" t="n">
         <v>0.001</v>
       </c>
       <c r="I12" t="n">
-        <v>498.1335897537959</v>
+        <v>498.1335897537953</v>
       </c>
       <c r="J12" t="n">
         <v>1721.762620415201</v>
       </c>
       <c r="K12" t="n">
-        <v>7.394514241080932</v>
+        <v>7.394514241080915</v>
       </c>
     </row>
     <row r="13">
@@ -903,25 +903,25 @@
         <v>62</v>
       </c>
       <c r="E13" t="n">
-        <v>0.2794460989117293</v>
+        <v>0.2794460989117291</v>
       </c>
       <c r="F13" t="n">
-        <v>0.2151109291717053</v>
+        <v>0.215110929171705</v>
       </c>
       <c r="G13" t="n">
-        <v>4.343597755954634</v>
+        <v>4.343597755954629</v>
       </c>
       <c r="H13" t="n">
         <v>0.001</v>
       </c>
       <c r="I13" t="n">
-        <v>506.8889733138345</v>
+        <v>506.888973313834</v>
       </c>
       <c r="J13" t="n">
         <v>1813.906063773498</v>
       </c>
       <c r="K13" t="n">
-        <v>7.070405377868608</v>
+        <v>7.070405377868595</v>
       </c>
     </row>
     <row r="14">
@@ -946,19 +946,19 @@
         <v>0.2060632065976186</v>
       </c>
       <c r="G14" t="n">
-        <v>4.426008656724396</v>
+        <v>4.426008656724394</v>
       </c>
       <c r="H14" t="n">
         <v>0.001</v>
       </c>
       <c r="I14" t="n">
-        <v>520.0013463685009</v>
+        <v>520.0013463685008</v>
       </c>
       <c r="J14" t="n">
         <v>1953.350649935113</v>
       </c>
       <c r="K14" t="n">
-        <v>6.638738296098122</v>
+        <v>6.638738296098114</v>
       </c>
     </row>
     <row r="15">
@@ -977,25 +977,25 @@
         <v>72</v>
       </c>
       <c r="E15" t="n">
-        <v>0.2346826155705923</v>
+        <v>0.2346826155705918</v>
       </c>
       <c r="F15" t="n">
-        <v>0.1767040258410918</v>
+        <v>0.1767040258410912</v>
       </c>
       <c r="G15" t="n">
-        <v>4.047746188127467</v>
+        <v>4.047746188127459</v>
       </c>
       <c r="H15" t="n">
         <v>0.001</v>
       </c>
       <c r="I15" t="n">
-        <v>486.4548087603548</v>
+        <v>486.4548087603538</v>
       </c>
       <c r="J15" t="n">
         <v>2072.819955485922</v>
       </c>
       <c r="K15" t="n">
-        <v>5.8398299769993</v>
+        <v>5.839829976999286</v>
       </c>
     </row>
     <row r="16">
@@ -1014,25 +1014,25 @@
         <v>76</v>
       </c>
       <c r="E16" t="n">
-        <v>0.2323611456709237</v>
+        <v>0.2323611456709234</v>
       </c>
       <c r="F16" t="n">
-        <v>0.1775297989331326</v>
+        <v>0.1775297989331323</v>
       </c>
       <c r="G16" t="n">
-        <v>4.237742814928424</v>
+        <v>4.237742814928419</v>
       </c>
       <c r="H16" t="n">
         <v>0.001</v>
       </c>
       <c r="I16" t="n">
-        <v>496.2224308025022</v>
+        <v>496.2224308025017</v>
       </c>
       <c r="J16" t="n">
         <v>2135.565433582714</v>
       </c>
       <c r="K16" t="n">
-        <v>5.669571852455076</v>
+        <v>5.669571852455072</v>
       </c>
     </row>
     <row r="17">
@@ -1051,25 +1051,25 @@
         <v>81</v>
       </c>
       <c r="E17" t="n">
-        <v>0.2324913222434052</v>
+        <v>0.2324913222434055</v>
       </c>
       <c r="F17" t="n">
-        <v>0.1813240770596322</v>
+        <v>0.1813240770596326</v>
       </c>
       <c r="G17" t="n">
-        <v>4.543752969470725</v>
+        <v>4.543752969470733</v>
       </c>
       <c r="H17" t="n">
         <v>0.001</v>
       </c>
       <c r="I17" t="n">
-        <v>525.9191440067963</v>
+        <v>525.9191440067971</v>
       </c>
       <c r="J17" t="n">
         <v>2262.102253675468</v>
       </c>
       <c r="K17" t="n">
-        <v>5.725451480651313</v>
+        <v>5.725451480651319</v>
       </c>
     </row>
     <row r="18">
@@ -1088,25 +1088,25 @@
         <v>86</v>
       </c>
       <c r="E18" t="n">
-        <v>0.2329768550408525</v>
+        <v>0.2329768550408528</v>
       </c>
       <c r="F18" t="n">
-        <v>0.1850379084809057</v>
+        <v>0.1850379084809062</v>
       </c>
       <c r="G18" t="n">
-        <v>4.859865970344581</v>
+        <v>4.859865970344588</v>
       </c>
       <c r="H18" t="n">
         <v>0.001</v>
       </c>
       <c r="I18" t="n">
-        <v>545.9729369709576</v>
+        <v>545.9729369709584</v>
       </c>
       <c r="J18" t="n">
         <v>2343.464276205554</v>
       </c>
       <c r="K18" t="n">
-        <v>5.564041607145965</v>
+        <v>5.564041607145979</v>
       </c>
     </row>
     <row r="19">
@@ -1125,25 +1125,25 @@
         <v>90</v>
       </c>
       <c r="E19" t="n">
-        <v>0.2224747594224214</v>
+        <v>0.2224747594224215</v>
       </c>
       <c r="F19" t="n">
         <v>0.1761934951023275</v>
       </c>
       <c r="G19" t="n">
-        <v>4.807015596715871</v>
+        <v>4.807015596715873</v>
       </c>
       <c r="H19" t="n">
         <v>0.001</v>
       </c>
       <c r="I19" t="n">
-        <v>550.5707756198966</v>
+        <v>550.5707756198968</v>
       </c>
       <c r="J19" t="n">
         <v>2474.756134355478</v>
       </c>
       <c r="K19" t="n">
-        <v>5.246150758657549</v>
+        <v>5.24615075865755</v>
       </c>
     </row>
     <row r="20">
@@ -1162,25 +1162,25 @@
         <v>95</v>
       </c>
       <c r="E20" t="n">
-        <v>0.2279835395489325</v>
+        <v>0.2279835395489326</v>
       </c>
       <c r="F20" t="n">
-        <v>0.1846118282876366</v>
+        <v>0.1846118282876367</v>
       </c>
       <c r="G20" t="n">
-        <v>5.256503211861519</v>
+        <v>5.256503211861522</v>
       </c>
       <c r="H20" t="n">
         <v>0.001</v>
       </c>
       <c r="I20" t="n">
-        <v>591.9513970181736</v>
+        <v>591.9513970181738</v>
       </c>
       <c r="J20" t="n">
         <v>2596.465508822938</v>
       </c>
       <c r="K20" t="n">
-        <v>5.353943655071094</v>
+        <v>5.353943655071093</v>
       </c>
     </row>
     <row r="21">
@@ -1199,25 +1199,25 @@
         <v>100</v>
       </c>
       <c r="E21" t="n">
-        <v>0.2141315808957042</v>
+        <v>0.2141315808957047</v>
       </c>
       <c r="F21" t="n">
-        <v>0.1723300692412204</v>
+        <v>0.172330069241221</v>
       </c>
       <c r="G21" t="n">
-        <v>5.122579840309089</v>
+        <v>5.1225798403091</v>
       </c>
       <c r="H21" t="n">
         <v>0.001</v>
       </c>
       <c r="I21" t="n">
-        <v>584.9491316892035</v>
+        <v>584.9491316892047</v>
       </c>
       <c r="J21" t="n">
         <v>2731.727516522241</v>
       </c>
       <c r="K21" t="n">
-        <v>4.985494666598608</v>
+        <v>4.985494666598618</v>
       </c>
     </row>
     <row r="22">
@@ -1236,25 +1236,25 @@
         <v>104</v>
       </c>
       <c r="E22" t="n">
-        <v>0.2232963412792216</v>
+        <v>0.2232963412792219</v>
       </c>
       <c r="F22" t="n">
-        <v>0.183668603589386</v>
+        <v>0.1836686035893864</v>
       </c>
       <c r="G22" t="n">
-        <v>5.634849585079805</v>
+        <v>5.634849585079812</v>
       </c>
       <c r="H22" t="n">
         <v>0.001</v>
       </c>
       <c r="I22" t="n">
-        <v>635.6780566370652</v>
+        <v>635.678056637066</v>
       </c>
       <c r="J22" t="n">
         <v>2846.791187868947</v>
       </c>
       <c r="K22" t="n">
-        <v>5.342279290739271</v>
+        <v>5.342279290739274</v>
       </c>
     </row>
     <row r="23">
@@ -1273,25 +1273,25 @@
         <v>109</v>
       </c>
       <c r="E23" t="n">
-        <v>0.2185174809382152</v>
+        <v>0.2185174809382151</v>
       </c>
       <c r="F23" t="n">
-        <v>0.1805814363235655</v>
+        <v>0.1805814363235654</v>
       </c>
       <c r="G23" t="n">
-        <v>5.760154574834887</v>
+        <v>5.760154574834885</v>
       </c>
       <c r="H23" t="n">
         <v>0.001</v>
       </c>
       <c r="I23" t="n">
-        <v>655.3893111570945</v>
+        <v>655.3893111570943</v>
       </c>
       <c r="J23" t="n">
         <v>2999.253461751203</v>
       </c>
       <c r="K23" t="n">
-        <v>5.29944841339681</v>
+        <v>5.299448413396805</v>
       </c>
     </row>
     <row r="24">
@@ -1310,25 +1310,25 @@
         <v>114</v>
       </c>
       <c r="E24" t="n">
-        <v>0.2208582366458276</v>
+        <v>0.220858236645828</v>
       </c>
       <c r="F24" t="n">
-        <v>0.1847868587127641</v>
+        <v>0.1847868587127646</v>
       </c>
       <c r="G24" t="n">
-        <v>6.122811195504285</v>
+        <v>6.122811195504295</v>
       </c>
       <c r="H24" t="n">
         <v>0.001</v>
       </c>
       <c r="I24" t="n">
-        <v>705.6293275768192</v>
+        <v>705.6293275768203</v>
       </c>
       <c r="J24" t="n">
         <v>3194.942322700781</v>
       </c>
       <c r="K24" t="n">
-        <v>5.398015944144059</v>
+        <v>5.398015944144066</v>
       </c>
     </row>
     <row r="25">
@@ -1347,25 +1347,25 @@
         <v>118</v>
       </c>
       <c r="E25" t="n">
-        <v>0.2061241458806004</v>
+        <v>0.2061241458806003</v>
       </c>
       <c r="F25" t="n">
-        <v>0.1706832595359844</v>
+        <v>0.1706832595359842</v>
       </c>
       <c r="G25" t="n">
-        <v>5.815998614603314</v>
+        <v>5.815998614603307</v>
       </c>
       <c r="H25" t="n">
         <v>0.001</v>
       </c>
       <c r="I25" t="n">
-        <v>678.8132858778263</v>
+        <v>678.8132858778257</v>
       </c>
       <c r="J25" t="n">
         <v>3293.225463605006</v>
       </c>
       <c r="K25" t="n">
-        <v>4.960461723362691</v>
+        <v>4.960461723362688</v>
       </c>
     </row>
     <row r="26">
@@ -1402,7 +1402,7 @@
         <v>3396.016992345067</v>
       </c>
       <c r="K26" t="n">
-        <v>4.853376658121172</v>
+        <v>4.853376658121173</v>
       </c>
     </row>
     <row r="27">
@@ -1421,25 +1421,25 @@
         <v>128</v>
       </c>
       <c r="E27" t="n">
-        <v>0.1918685918658002</v>
+        <v>0.1918685918658001</v>
       </c>
       <c r="F27" t="n">
-        <v>0.1587484521881691</v>
+        <v>0.158748452188169</v>
       </c>
       <c r="G27" t="n">
-        <v>5.793109380978409</v>
+        <v>5.793109380978406</v>
       </c>
       <c r="H27" t="n">
         <v>0.001</v>
       </c>
       <c r="I27" t="n">
-        <v>676.0836276193374</v>
+        <v>676.0836276193372</v>
       </c>
       <c r="J27" t="n">
         <v>3523.680562018274</v>
       </c>
       <c r="K27" t="n">
-        <v>4.492789531176011</v>
+        <v>4.492789531176012</v>
       </c>
     </row>
     <row r="28">
@@ -1458,25 +1458,25 @@
         <v>132</v>
       </c>
       <c r="E28" t="n">
-        <v>0.1912461827455566</v>
+        <v>0.1912461827455567</v>
       </c>
       <c r="F28" t="n">
-        <v>0.1591527772989516</v>
+        <v>0.1591527772989517</v>
       </c>
       <c r="G28" t="n">
-        <v>5.959049221614721</v>
+        <v>5.959049221614723</v>
       </c>
       <c r="H28" t="n">
         <v>0.001</v>
       </c>
       <c r="I28" t="n">
-        <v>697.0485726523988</v>
+        <v>697.0485726523991</v>
       </c>
       <c r="J28" t="n">
         <v>3644.77116690892</v>
       </c>
       <c r="K28" t="n">
-        <v>4.512053297405028</v>
+        <v>4.51205329740503</v>
       </c>
     </row>
     <row r="29">
@@ -1495,25 +1495,25 @@
         <v>137</v>
       </c>
       <c r="E29" t="n">
-        <v>0.1837642497820642</v>
+        <v>0.1837642497820643</v>
       </c>
       <c r="F29" t="n">
-        <v>0.1526102135142041</v>
+        <v>0.1526102135142043</v>
       </c>
       <c r="G29" t="n">
-        <v>5.898569552980951</v>
+        <v>5.898569552980956</v>
       </c>
       <c r="H29" t="n">
         <v>0.001</v>
       </c>
       <c r="I29" t="n">
-        <v>692.1452534146133</v>
+        <v>692.1452534146139</v>
       </c>
       <c r="J29" t="n">
         <v>3766.484799058931</v>
       </c>
       <c r="K29" t="n">
-        <v>4.283247081278815</v>
+        <v>4.283247081278818</v>
       </c>
     </row>
     <row r="30">
@@ -1532,25 +1532,25 @@
         <v>142</v>
       </c>
       <c r="E30" t="n">
-        <v>0.1788636025916063</v>
+        <v>0.1788636025916064</v>
       </c>
       <c r="F30" t="n">
-        <v>0.1486747644515918</v>
+        <v>0.1486747644515919</v>
       </c>
       <c r="G30" t="n">
-        <v>5.924825651190845</v>
+        <v>5.924825651190848</v>
       </c>
       <c r="H30" t="n">
         <v>0.001</v>
       </c>
       <c r="I30" t="n">
-        <v>690.698206216877</v>
+        <v>690.6982062168773</v>
       </c>
       <c r="J30" t="n">
         <v>3861.591716867779</v>
       </c>
       <c r="K30" t="n">
-        <v>4.088189128688913</v>
+        <v>4.088189128688915</v>
       </c>
     </row>
     <row r="31">
@@ -1569,25 +1569,25 @@
         <v>146</v>
       </c>
       <c r="E31" t="n">
-        <v>0.1742823078008449</v>
+        <v>0.1742823078008453</v>
       </c>
       <c r="F31" t="n">
-        <v>0.1447923902223035</v>
+        <v>0.1447923902223039</v>
       </c>
       <c r="G31" t="n">
-        <v>5.909894706781544</v>
+        <v>5.909894706781558</v>
       </c>
       <c r="H31" t="n">
         <v>0.001</v>
       </c>
       <c r="I31" t="n">
-        <v>695.2930456525405</v>
+        <v>695.2930456525422</v>
       </c>
       <c r="J31" t="n">
         <v>3989.464303210069</v>
       </c>
       <c r="K31" t="n">
-        <v>3.948111421122615</v>
+        <v>3.948111421122626</v>
       </c>
     </row>
     <row r="32">
@@ -1612,13 +1612,13 @@
         <v>0.1423253379499558</v>
       </c>
       <c r="G32" t="n">
-        <v>5.978298097664378</v>
+        <v>5.97829809766438</v>
       </c>
       <c r="H32" t="n">
         <v>0.001</v>
       </c>
       <c r="I32" t="n">
-        <v>704.2853859298878</v>
+        <v>704.2853859298879</v>
       </c>
       <c r="J32" t="n">
         <v>4120.688492350118</v>
@@ -1643,25 +1643,25 @@
         <v>156</v>
       </c>
       <c r="E33" t="n">
-        <v>0.1659421902880722</v>
+        <v>0.1659421902880719</v>
       </c>
       <c r="F33" t="n">
-        <v>0.1381402632976746</v>
+        <v>0.1381402632976741</v>
       </c>
       <c r="G33" t="n">
-        <v>5.968729805865125</v>
+        <v>5.968729805865116</v>
       </c>
       <c r="H33" t="n">
         <v>0.001</v>
       </c>
       <c r="I33" t="n">
-        <v>704.1443420415306</v>
+        <v>704.1443420415294</v>
       </c>
       <c r="J33" t="n">
         <v>4243.311124308717</v>
       </c>
       <c r="K33" t="n">
-        <v>3.704027719384896</v>
+        <v>3.704027719384889</v>
       </c>
     </row>
     <row r="34">
@@ -1680,25 +1680,25 @@
         <v>160</v>
       </c>
       <c r="E34" t="n">
-        <v>0.1626770151973614</v>
+        <v>0.1626770151973615</v>
       </c>
       <c r="F34" t="n">
         <v>0.1354912040024705</v>
       </c>
       <c r="G34" t="n">
-        <v>5.983894099431324</v>
+        <v>5.983894099431325</v>
       </c>
       <c r="H34" t="n">
         <v>0.001</v>
       </c>
       <c r="I34" t="n">
-        <v>703.0416022242491</v>
+        <v>703.0416022242492</v>
       </c>
       <c r="J34" t="n">
         <v>4321.702124736625</v>
       </c>
       <c r="K34" t="n">
-        <v>3.578043486341032</v>
+        <v>3.578043486341034</v>
       </c>
     </row>
     <row r="35">
@@ -1720,22 +1720,22 @@
         <v>0.1694369337011029</v>
       </c>
       <c r="F35" t="n">
-        <v>0.1433185982828985</v>
+        <v>0.1433185982828986</v>
       </c>
       <c r="G35" t="n">
-        <v>6.487279184836808</v>
+        <v>6.487279184836812</v>
       </c>
       <c r="H35" t="n">
         <v>0.001</v>
       </c>
       <c r="I35" t="n">
-        <v>757.6297216340314</v>
+        <v>757.6297216340317</v>
       </c>
       <c r="J35" t="n">
         <v>4471.455573969113</v>
       </c>
       <c r="K35" t="n">
-        <v>3.784850847895306</v>
+        <v>3.784850847895308</v>
       </c>
     </row>
     <row r="36">
@@ -1757,22 +1757,22 @@
         <v>0.171514080247389</v>
       </c>
       <c r="F36" t="n">
-        <v>0.1462553631817605</v>
+        <v>0.1462553631817606</v>
       </c>
       <c r="G36" t="n">
-        <v>6.79029262657137</v>
+        <v>6.790292626571371</v>
       </c>
       <c r="H36" t="n">
         <v>0.001</v>
       </c>
       <c r="I36" t="n">
-        <v>783.6740135721458</v>
+        <v>783.6740135721459</v>
       </c>
       <c r="J36" t="n">
         <v>4569.152645903986</v>
       </c>
       <c r="K36" t="n">
-        <v>3.807085593098886</v>
+        <v>3.80708559309889</v>
       </c>
     </row>
     <row r="37">
@@ -1791,25 +1791,25 @@
         <v>174</v>
       </c>
       <c r="E37" t="n">
-        <v>0.1693885902118238</v>
+        <v>0.1693885902118237</v>
       </c>
       <c r="F37" t="n">
         <v>0.1446680125395566</v>
       </c>
       <c r="G37" t="n">
-        <v>6.852129123254788</v>
+        <v>6.852129123254785</v>
       </c>
       <c r="H37" t="n">
         <v>0.001</v>
       </c>
       <c r="I37" t="n">
-        <v>789.659765834765</v>
+        <v>789.6597658347648</v>
       </c>
       <c r="J37" t="n">
         <v>4661.82382678361</v>
       </c>
       <c r="K37" t="n">
-        <v>3.760511996712129</v>
+        <v>3.760511996712126</v>
       </c>
     </row>
     <row r="38">
@@ -1831,22 +1831,22 @@
         <v>0.177518171400859</v>
       </c>
       <c r="F38" t="n">
-        <v>0.1537470202852768</v>
+        <v>0.1537470202852769</v>
       </c>
       <c r="G38" t="n">
-        <v>7.467798700101438</v>
+        <v>7.467798700101443</v>
       </c>
       <c r="H38" t="n">
         <v>0.001</v>
       </c>
       <c r="I38" t="n">
-        <v>849.3642340867136</v>
+        <v>849.364234086714</v>
       </c>
       <c r="J38" t="n">
         <v>4784.660789281901</v>
       </c>
       <c r="K38" t="n">
-        <v>4.007356341706267</v>
+        <v>4.007356341706271</v>
       </c>
     </row>
     <row r="39">
@@ -1865,25 +1865,25 @@
         <v>184</v>
       </c>
       <c r="E39" t="n">
-        <v>0.1830762476806237</v>
+        <v>0.1830762476806235</v>
       </c>
       <c r="F39" t="n">
-        <v>0.1601289512671581</v>
+        <v>0.160128951267158</v>
       </c>
       <c r="G39" t="n">
-        <v>7.978118397128187</v>
+        <v>7.978118397128177</v>
       </c>
       <c r="H39" t="n">
         <v>0.001</v>
       </c>
       <c r="I39" t="n">
-        <v>903.0324416441865</v>
+        <v>903.0324416441856</v>
       </c>
       <c r="J39" t="n">
         <v>4932.548340293305</v>
       </c>
       <c r="K39" t="n">
-        <v>4.249461513966827</v>
+        <v>4.24946151396682</v>
       </c>
     </row>
     <row r="40">
@@ -1902,25 +1902,25 @@
         <v>188</v>
       </c>
       <c r="E40" t="n">
-        <v>0.178127556986401</v>
+        <v>0.1781275569864013</v>
       </c>
       <c r="F40" t="n">
-        <v>0.1555486437167968</v>
+        <v>0.155548643716797</v>
       </c>
       <c r="G40" t="n">
-        <v>7.889111174637248</v>
+        <v>7.88911117463726</v>
       </c>
       <c r="H40" t="n">
         <v>0.001</v>
       </c>
       <c r="I40" t="n">
-        <v>903.3243832460298</v>
+        <v>903.3243832460312</v>
       </c>
       <c r="J40" t="n">
         <v>5071.221985686321</v>
       </c>
       <c r="K40" t="n">
-        <v>4.153582946122671</v>
+        <v>4.153582946122677</v>
       </c>
     </row>
     <row r="41">
@@ -1939,25 +1939,25 @@
         <v>193</v>
       </c>
       <c r="E41" t="n">
-        <v>0.1796612794507078</v>
+        <v>0.1796612794507079</v>
       </c>
       <c r="F41" t="n">
-        <v>0.1577270890616892</v>
+        <v>0.1577270890616894</v>
       </c>
       <c r="G41" t="n">
-        <v>8.190923679620123</v>
+        <v>8.190923679620131</v>
       </c>
       <c r="H41" t="n">
         <v>0.001</v>
       </c>
       <c r="I41" t="n">
-        <v>929.8807269639422</v>
+        <v>929.8807269639427</v>
       </c>
       <c r="J41" t="n">
         <v>5175.743653874322</v>
       </c>
       <c r="K41" t="n">
-        <v>4.149894283544993</v>
+        <v>4.149894283544994</v>
       </c>
     </row>
     <row r="42">
@@ -1982,19 +1982,19 @@
         <v>0.1581754298587027</v>
       </c>
       <c r="G42" t="n">
-        <v>8.40310054788119</v>
+        <v>8.403100547881191</v>
       </c>
       <c r="H42" t="n">
         <v>0.001</v>
       </c>
       <c r="I42" t="n">
-        <v>943.4414661298528</v>
+        <v>943.4414661298529</v>
       </c>
       <c r="J42" t="n">
         <v>5254.725389600355</v>
       </c>
       <c r="K42" t="n">
-        <v>4.150818474203917</v>
+        <v>4.150818474203922</v>
       </c>
     </row>
     <row r="43">
@@ -2013,25 +2013,25 @@
         <v>202</v>
       </c>
       <c r="E43" t="n">
-        <v>0.1812747727109276</v>
+        <v>0.1812747727109282</v>
       </c>
       <c r="F43" t="n">
-        <v>0.1603889250760023</v>
+        <v>0.1603889250760029</v>
       </c>
       <c r="G43" t="n">
-        <v>8.679311267587718</v>
+        <v>8.679311267587746</v>
       </c>
       <c r="H43" t="n">
         <v>0.001</v>
       </c>
       <c r="I43" t="n">
-        <v>981.2860328532058</v>
+        <v>981.286032853209</v>
       </c>
       <c r="J43" t="n">
         <v>5413.25203820847</v>
       </c>
       <c r="K43" t="n">
-        <v>4.266463213271095</v>
+        <v>4.266463213271111</v>
       </c>
     </row>
     <row r="44">
@@ -2050,25 +2050,25 @@
         <v>207</v>
       </c>
       <c r="E44" t="n">
-        <v>0.1792090753792349</v>
+        <v>0.1792090753792352</v>
       </c>
       <c r="F44" t="n">
-        <v>0.1587913906871761</v>
+        <v>0.1587913906871763</v>
       </c>
       <c r="G44" t="n">
-        <v>8.777149715165097</v>
+        <v>8.777149715165111</v>
       </c>
       <c r="H44" t="n">
         <v>0.001</v>
       </c>
       <c r="I44" t="n">
-        <v>987.7082951914917</v>
+        <v>987.7082951914931</v>
       </c>
       <c r="J44" t="n">
         <v>5511.485917224581</v>
       </c>
       <c r="K44" t="n">
-        <v>4.179563987248719</v>
+        <v>4.179563987248722</v>
       </c>
     </row>
     <row r="45">
@@ -2087,25 +2087,25 @@
         <v>212</v>
       </c>
       <c r="E45" t="n">
-        <v>0.1827729557245516</v>
+        <v>0.1827729557245518</v>
       </c>
       <c r="F45" t="n">
-        <v>0.1629373478537883</v>
+        <v>0.1629373478537886</v>
       </c>
       <c r="G45" t="n">
-        <v>9.214386416357314</v>
+        <v>9.214386416357321</v>
       </c>
       <c r="H45" t="n">
         <v>0.001</v>
       </c>
       <c r="I45" t="n">
-        <v>1038.66548470414</v>
+        <v>1038.665484704141</v>
       </c>
       <c r="J45" t="n">
         <v>5682.818229790315</v>
       </c>
       <c r="K45" t="n">
-        <v>4.284264848007721</v>
+        <v>4.284264848007727</v>
       </c>
     </row>
     <row r="46">
@@ -2124,10 +2124,10 @@
         <v>216</v>
       </c>
       <c r="E46" t="n">
-        <v>0.1864715475029138</v>
+        <v>0.1864715475029139</v>
       </c>
       <c r="F46" t="n">
-        <v>0.1671018224434595</v>
+        <v>0.1671018224434596</v>
       </c>
       <c r="G46" t="n">
         <v>9.62695892329646</v>
@@ -2142,7 +2142,7 @@
         <v>5784.59235442906</v>
       </c>
       <c r="K46" t="n">
-        <v>4.383673373597493</v>
+        <v>4.383673373597494</v>
       </c>
     </row>
     <row r="47">
@@ -2161,25 +2161,25 @@
         <v>221</v>
       </c>
       <c r="E47" t="n">
-        <v>0.1892552850394252</v>
+        <v>0.1892552850394244</v>
       </c>
       <c r="F47" t="n">
-        <v>0.170400756784528</v>
+        <v>0.1704007567845274</v>
       </c>
       <c r="G47" t="n">
-        <v>10.03765686846447</v>
+        <v>10.03765686846443</v>
       </c>
       <c r="H47" t="n">
         <v>0.001</v>
       </c>
       <c r="I47" t="n">
-        <v>1113.660895912228</v>
+        <v>1113.660895912224</v>
       </c>
       <c r="J47" t="n">
         <v>5884.437497638352</v>
       </c>
       <c r="K47" t="n">
-        <v>4.436159608725049</v>
+        <v>4.436159608725032</v>
       </c>
     </row>
     <row r="48">
@@ -2198,25 +2198,25 @@
         <v>226</v>
       </c>
       <c r="E48" t="n">
-        <v>0.1827320963727194</v>
+        <v>0.1827320963727195</v>
       </c>
       <c r="F48" t="n">
-        <v>0.1641578258357357</v>
+        <v>0.1641578258357358</v>
       </c>
       <c r="G48" t="n">
-        <v>9.837915088448691</v>
+        <v>9.8379150884487</v>
       </c>
       <c r="H48" t="n">
         <v>0.001</v>
       </c>
       <c r="I48" t="n">
-        <v>1086.777967975352</v>
+        <v>1086.777967975353</v>
       </c>
       <c r="J48" t="n">
         <v>5947.384118872291</v>
       </c>
       <c r="K48" t="n">
-        <v>4.239419664537198</v>
+        <v>4.239419664537203</v>
       </c>
     </row>
     <row r="49">
@@ -2235,25 +2235,25 @@
         <v>230</v>
       </c>
       <c r="E49" t="n">
-        <v>0.1836871092610972</v>
+        <v>0.1836871092610974</v>
       </c>
       <c r="F49" t="n">
-        <v>0.1654658393785324</v>
+        <v>0.1654658393785327</v>
       </c>
       <c r="G49" t="n">
-        <v>10.080916996727</v>
+        <v>10.08091699672701</v>
       </c>
       <c r="H49" t="n">
         <v>0.001</v>
       </c>
       <c r="I49" t="n">
-        <v>1112.638782561442</v>
+        <v>1112.638782561444</v>
       </c>
       <c r="J49" t="n">
         <v>6057.250217705322</v>
       </c>
       <c r="K49" t="n">
-        <v>4.265071278523673</v>
+        <v>4.265071278523682</v>
       </c>
     </row>
     <row r="50">
@@ -2272,25 +2272,25 @@
         <v>11</v>
       </c>
       <c r="E50" t="n">
-        <v>0.4540647766946757</v>
+        <v>0.4540647766946753</v>
       </c>
       <c r="F50" t="n">
-        <v>-0.09187044661064858</v>
+        <v>-0.09187044661064947</v>
       </c>
       <c r="G50" t="n">
-        <v>0.831719144160682</v>
+        <v>0.8317191441606815</v>
       </c>
       <c r="H50" t="n">
         <v>0.663</v>
       </c>
       <c r="I50" t="n">
-        <v>155.8593159772077</v>
+        <v>155.8593159772076</v>
       </c>
       <c r="J50" t="n">
         <v>343.25348271181</v>
       </c>
       <c r="K50" t="n">
-        <v>9.152322810631688</v>
+        <v>9.152322810631675</v>
       </c>
     </row>
     <row r="51">
@@ -2309,10 +2309,10 @@
         <v>16</v>
       </c>
       <c r="E51" t="n">
-        <v>0.3375533790435991</v>
+        <v>0.337553379043599</v>
       </c>
       <c r="F51" t="n">
-        <v>0.006330068565398639</v>
+        <v>0.006330068565398417</v>
       </c>
       <c r="G51" t="n">
         <v>1.019111180780905</v>
@@ -2346,10 +2346,10 @@
         <v>20</v>
       </c>
       <c r="E52" t="n">
-        <v>0.2690628190827336</v>
+        <v>0.2690628190827337</v>
       </c>
       <c r="F52" t="n">
-        <v>0.008013825897995486</v>
+        <v>0.008013825897995597</v>
       </c>
       <c r="G52" t="n">
         <v>1.030698551257481</v>
@@ -2358,13 +2358,13 @@
         <v>0.45</v>
       </c>
       <c r="I52" t="n">
-        <v>148.9924651300704</v>
+        <v>148.9924651300705</v>
       </c>
       <c r="J52" t="n">
         <v>553.7460197510866</v>
       </c>
       <c r="K52" t="n">
-        <v>4.669555028397693</v>
+        <v>4.669555028397697</v>
       </c>
     </row>
     <row r="53">
@@ -2383,25 +2383,25 @@
         <v>25</v>
       </c>
       <c r="E53" t="n">
-        <v>0.2490882289063758</v>
+        <v>0.2490882289063756</v>
       </c>
       <c r="F53" t="n">
-        <v>0.05147986809226424</v>
+        <v>0.05147986809226401</v>
       </c>
       <c r="G53" t="n">
-        <v>1.26051462539427</v>
+        <v>1.260514625394269</v>
       </c>
       <c r="H53" t="n">
         <v>0.173</v>
       </c>
       <c r="I53" t="n">
-        <v>177.0048403230227</v>
+        <v>177.0048403230225</v>
       </c>
       <c r="J53" t="n">
         <v>710.6110196381584</v>
       </c>
       <c r="K53" t="n">
-        <v>3.981816140151961</v>
+        <v>3.981816140151957</v>
       </c>
     </row>
     <row r="54">
@@ -2420,25 +2420,25 @@
         <v>30</v>
       </c>
       <c r="E54" t="n">
-        <v>0.2290282931613526</v>
+        <v>0.2290282931613529</v>
       </c>
       <c r="F54" t="n">
-        <v>0.06840918756996783</v>
+        <v>0.06840918756996806</v>
       </c>
       <c r="G54" t="n">
-        <v>1.42590940422742</v>
+        <v>1.425909404227422</v>
       </c>
       <c r="H54" t="n">
         <v>0.082</v>
       </c>
       <c r="I54" t="n">
-        <v>187.9845131799058</v>
+        <v>187.9845131799059</v>
       </c>
       <c r="J54" t="n">
         <v>820.7916610873438</v>
       </c>
       <c r="K54" t="n">
-        <v>3.660958835599072</v>
+        <v>3.660958835599077</v>
       </c>
     </row>
     <row r="55">
@@ -2475,7 +2475,7 @@
         <v>885.4275528238688</v>
       </c>
       <c r="K55" t="n">
-        <v>3.447740269724833</v>
+        <v>3.447740269724831</v>
       </c>
     </row>
     <row r="56">
@@ -2494,25 +2494,25 @@
         <v>39</v>
       </c>
       <c r="E56" t="n">
-        <v>0.2041629597528988</v>
+        <v>0.2041629597528989</v>
       </c>
       <c r="F56" t="n">
-        <v>0.08358159001848942</v>
+        <v>0.08358159001848953</v>
       </c>
       <c r="G56" t="n">
-        <v>1.693155088572846</v>
+        <v>1.693155088572847</v>
       </c>
       <c r="H56" t="n">
         <v>0.026</v>
       </c>
       <c r="I56" t="n">
-        <v>194.4687604532767</v>
+        <v>194.4687604532768</v>
       </c>
       <c r="J56" t="n">
         <v>952.5173454021478</v>
       </c>
       <c r="K56" t="n">
-        <v>3.037457404256477</v>
+        <v>3.037457404256481</v>
       </c>
     </row>
     <row r="57">
@@ -2531,25 +2531,25 @@
         <v>44</v>
       </c>
       <c r="E57" t="n">
-        <v>0.2171090769975937</v>
+        <v>0.2171090769975938</v>
       </c>
       <c r="F57" t="n">
-        <v>0.1140971134446456</v>
+        <v>0.1140971134446457</v>
       </c>
       <c r="G57" t="n">
-        <v>2.107610315436805</v>
+        <v>2.107610315436806</v>
       </c>
       <c r="H57" t="n">
         <v>0.005</v>
       </c>
       <c r="I57" t="n">
-        <v>237.7647795625751</v>
+        <v>237.7647795625752</v>
       </c>
       <c r="J57" t="n">
         <v>1095.139746576373</v>
       </c>
       <c r="K57" t="n">
-        <v>3.535853256994267</v>
+        <v>3.535853256994268</v>
       </c>
     </row>
     <row r="58">
@@ -2568,25 +2568,25 @@
         <v>48</v>
       </c>
       <c r="E58" t="n">
-        <v>0.2164837485069394</v>
+        <v>0.2164837485069393</v>
       </c>
       <c r="F58" t="n">
-        <v>0.1232080042815751</v>
+        <v>0.123208004281575</v>
       </c>
       <c r="G58" t="n">
-        <v>2.320900790498022</v>
+        <v>2.320900790498021</v>
       </c>
       <c r="H58" t="n">
         <v>0.002</v>
       </c>
       <c r="I58" t="n">
-        <v>265.8135459136411</v>
+        <v>265.813545913641</v>
       </c>
       <c r="J58" t="n">
         <v>1227.868363084633</v>
       </c>
       <c r="K58" t="n">
-        <v>3.467782559166386</v>
+        <v>3.467782559166384</v>
       </c>
     </row>
     <row r="59">
@@ -2605,25 +2605,25 @@
         <v>53</v>
       </c>
       <c r="E59" t="n">
-        <v>0.2491154112060492</v>
+        <v>0.2491154112060493</v>
       </c>
       <c r="F59" t="n">
-        <v>0.1692340719726502</v>
+        <v>0.1692340719726503</v>
       </c>
       <c r="G59" t="n">
-        <v>3.118568286370092</v>
+        <v>3.118568286370094</v>
       </c>
       <c r="H59" t="n">
         <v>0.001</v>
       </c>
       <c r="I59" t="n">
-        <v>355.8637443138059</v>
+        <v>355.863744313806</v>
       </c>
       <c r="J59" t="n">
         <v>1428.509551420176</v>
       </c>
       <c r="K59" t="n">
-        <v>4.898928794356262</v>
+        <v>4.898928794356264</v>
       </c>
     </row>
     <row r="60">
@@ -2660,7 +2660,7 @@
         <v>1587.411905297559</v>
       </c>
       <c r="K60" t="n">
-        <v>5.421913695254554</v>
+        <v>5.421913695254558</v>
       </c>
     </row>
     <row r="61">
@@ -2679,25 +2679,25 @@
         <v>62</v>
       </c>
       <c r="E61" t="n">
-        <v>0.2596740034226861</v>
+        <v>0.2596740034226862</v>
       </c>
       <c r="F61" t="n">
-        <v>0.1935734680139974</v>
+        <v>0.1935734680139976</v>
       </c>
       <c r="G61" t="n">
-        <v>3.92847050053626</v>
+        <v>3.928470500536262</v>
       </c>
       <c r="H61" t="n">
         <v>0.001</v>
       </c>
       <c r="I61" t="n">
-        <v>450.9244023184472</v>
+        <v>450.9244023184474</v>
       </c>
       <c r="J61" t="n">
         <v>1736.501907680192</v>
       </c>
       <c r="K61" t="n">
-        <v>5.542146240870012</v>
+        <v>5.542146240870014</v>
       </c>
     </row>
     <row r="62">
@@ -2716,25 +2716,25 @@
         <v>67</v>
       </c>
       <c r="E62" t="n">
-        <v>0.2286852390593463</v>
+        <v>0.2286852390593461</v>
       </c>
       <c r="F62" t="n">
-        <v>0.1654627176707681</v>
+        <v>0.1654627176707678</v>
       </c>
       <c r="G62" t="n">
-        <v>3.617148352148144</v>
+        <v>3.617148352148141</v>
       </c>
       <c r="H62" t="n">
         <v>0.001</v>
       </c>
       <c r="I62" t="n">
-        <v>423.7689487047987</v>
+        <v>423.7689487047983</v>
       </c>
       <c r="J62" t="n">
         <v>1853.066470087412</v>
       </c>
       <c r="K62" t="n">
-        <v>4.831600427020528</v>
+        <v>4.831600427020523</v>
       </c>
     </row>
     <row r="63">
@@ -2753,25 +2753,25 @@
         <v>72</v>
       </c>
       <c r="E63" t="n">
-        <v>0.2007699431303814</v>
+        <v>0.2007699431303815</v>
       </c>
       <c r="F63" t="n">
-        <v>0.1402222115493497</v>
+        <v>0.1402222115493499</v>
       </c>
       <c r="G63" t="n">
-        <v>3.315895375232822</v>
+        <v>3.315895375232826</v>
       </c>
       <c r="H63" t="n">
         <v>0.001</v>
       </c>
       <c r="I63" t="n">
-        <v>400.7771584283191</v>
+        <v>400.7771584283195</v>
       </c>
       <c r="J63" t="n">
         <v>1996.200985961587</v>
       </c>
       <c r="K63" t="n">
-        <v>4.300665574403078</v>
+        <v>4.300665574403083</v>
       </c>
     </row>
     <row r="64">
@@ -2790,25 +2790,25 @@
         <v>76</v>
       </c>
       <c r="E64" t="n">
-        <v>0.2008168961751942</v>
+        <v>0.2008168961751941</v>
       </c>
       <c r="F64" t="n">
-        <v>0.1437323887591367</v>
+        <v>0.1437323887591366</v>
       </c>
       <c r="G64" t="n">
-        <v>3.517887869497593</v>
+        <v>3.51788786949759</v>
       </c>
       <c r="H64" t="n">
         <v>0.001</v>
       </c>
       <c r="I64" t="n">
-        <v>429.6952753753983</v>
+        <v>429.6952753753981</v>
       </c>
       <c r="J64" t="n">
         <v>2139.736663395737</v>
       </c>
       <c r="K64" t="n">
-        <v>4.405752670014368</v>
+        <v>4.405752670014369</v>
       </c>
     </row>
     <row r="65">
@@ -2827,25 +2827,25 @@
         <v>81</v>
       </c>
       <c r="E65" t="n">
-        <v>0.1794150350020619</v>
+        <v>0.179415035002062</v>
       </c>
       <c r="F65" t="n">
-        <v>0.124709370668866</v>
+        <v>0.1247093706688661</v>
       </c>
       <c r="G65" t="n">
-        <v>3.279642742464446</v>
+        <v>3.279642742464448</v>
       </c>
       <c r="H65" t="n">
         <v>0.001</v>
       </c>
       <c r="I65" t="n">
-        <v>407.3769694764212</v>
+        <v>407.3769694764215</v>
       </c>
       <c r="J65" t="n">
         <v>2270.584343568194</v>
       </c>
       <c r="K65" t="n">
-        <v>3.907193209204038</v>
+        <v>3.907193209204044</v>
       </c>
     </row>
     <row r="66">
@@ -2864,25 +2864,25 @@
         <v>86</v>
       </c>
       <c r="E66" t="n">
-        <v>0.177950035566393</v>
+        <v>0.1779500355663928</v>
       </c>
       <c r="F66" t="n">
-        <v>0.1265719127892926</v>
+        <v>0.1265719127892924</v>
       </c>
       <c r="G66" t="n">
-        <v>3.463537123347496</v>
+        <v>3.463537123347494</v>
       </c>
       <c r="H66" t="n">
         <v>0.001</v>
       </c>
       <c r="I66" t="n">
-        <v>423.0218300961287</v>
+        <v>423.0218300961284</v>
       </c>
       <c r="J66" t="n">
         <v>2377.19441162067</v>
       </c>
       <c r="K66" t="n">
-        <v>3.87588015521672</v>
+        <v>3.875880155216719</v>
       </c>
     </row>
     <row r="67">
@@ -2901,25 +2901,25 @@
         <v>90</v>
       </c>
       <c r="E67" t="n">
-        <v>0.1801093091118438</v>
+        <v>0.1801093091118439</v>
       </c>
       <c r="F67" t="n">
-        <v>0.1313062917970725</v>
+        <v>0.1313062917970728</v>
       </c>
       <c r="G67" t="n">
-        <v>3.690536344303656</v>
+        <v>3.690536344303659</v>
       </c>
       <c r="H67" t="n">
         <v>0.001</v>
       </c>
       <c r="I67" t="n">
-        <v>444.3413602864084</v>
+        <v>444.3413602864088</v>
       </c>
       <c r="J67" t="n">
         <v>2467.064931166232</v>
       </c>
       <c r="K67" t="n">
-        <v>3.990592698089621</v>
+        <v>3.990592698089626</v>
       </c>
     </row>
     <row r="68">
@@ -2938,19 +2938,19 @@
         <v>95</v>
       </c>
       <c r="E68" t="n">
-        <v>0.1812893623035286</v>
+        <v>0.1812893623035288</v>
       </c>
       <c r="F68" t="n">
-        <v>0.1352943826576596</v>
+        <v>0.1352943826576597</v>
       </c>
       <c r="G68" t="n">
-        <v>3.941503261863282</v>
+        <v>3.941503261863284</v>
       </c>
       <c r="H68" t="n">
         <v>0.001</v>
       </c>
       <c r="I68" t="n">
-        <v>471.4850423811629</v>
+        <v>471.4850423811632</v>
       </c>
       <c r="J68" t="n">
         <v>2600.731981128414</v>
@@ -2975,25 +2975,25 @@
         <v>100</v>
       </c>
       <c r="E69" t="n">
-        <v>0.1748967880624036</v>
+        <v>0.1748967880624035</v>
       </c>
       <c r="F69" t="n">
-        <v>0.1310083193423187</v>
+        <v>0.1310083193423186</v>
       </c>
       <c r="G69" t="n">
-        <v>3.98502825828518</v>
+        <v>3.985028258285178</v>
       </c>
       <c r="H69" t="n">
         <v>0.001</v>
       </c>
       <c r="I69" t="n">
-        <v>482.4602509001278</v>
+        <v>482.4602509001276</v>
       </c>
       <c r="J69" t="n">
         <v>2758.542659616967</v>
       </c>
       <c r="K69" t="n">
-        <v>3.915466250254441</v>
+        <v>3.915466250254436</v>
       </c>
     </row>
     <row r="70">
@@ -3012,25 +3012,25 @@
         <v>104</v>
       </c>
       <c r="E70" t="n">
-        <v>0.1693897411386434</v>
+        <v>0.1693897411386435</v>
       </c>
       <c r="F70" t="n">
-        <v>0.1270116667069415</v>
+        <v>0.1270116667069416</v>
       </c>
       <c r="G70" t="n">
-        <v>3.997108018950658</v>
+        <v>3.99710801895066</v>
       </c>
       <c r="H70" t="n">
         <v>0.001</v>
       </c>
       <c r="I70" t="n">
-        <v>480.3095104593776</v>
+        <v>480.3095104593779</v>
       </c>
       <c r="J70" t="n">
         <v>2835.528924188215</v>
       </c>
       <c r="K70" t="n">
-        <v>3.734636310543173</v>
+        <v>3.734636310543169</v>
       </c>
     </row>
     <row r="71">
@@ -3049,25 +3049,25 @@
         <v>109</v>
       </c>
       <c r="E71" t="n">
-        <v>0.1719684363777777</v>
+        <v>0.1719684363777775</v>
       </c>
       <c r="F71" t="n">
-        <v>0.1317727294058252</v>
+        <v>0.131772729405825</v>
       </c>
       <c r="G71" t="n">
-        <v>4.278278685277821</v>
+        <v>4.278278685277815</v>
       </c>
       <c r="H71" t="n">
         <v>0.001</v>
       </c>
       <c r="I71" t="n">
-        <v>512.6168055202986</v>
+        <v>512.6168055202979</v>
       </c>
       <c r="J71" t="n">
         <v>2980.877283748686</v>
       </c>
       <c r="K71" t="n">
-        <v>3.864156970198032</v>
+        <v>3.864156970198027</v>
       </c>
     </row>
     <row r="72">
@@ -3086,25 +3086,25 @@
         <v>114</v>
       </c>
       <c r="E72" t="n">
-        <v>0.1656348374493648</v>
+        <v>0.1656348374493649</v>
       </c>
       <c r="F72" t="n">
-        <v>0.1270068206646132</v>
+        <v>0.1270068206646133</v>
       </c>
       <c r="G72" t="n">
-        <v>4.287945673533749</v>
+        <v>4.287945673533751</v>
       </c>
       <c r="H72" t="n">
         <v>0.001</v>
       </c>
       <c r="I72" t="n">
-        <v>514.5086984406419</v>
+        <v>514.5086984406421</v>
       </c>
       <c r="J72" t="n">
         <v>3106.283112681106</v>
       </c>
       <c r="K72" t="n">
-        <v>3.729092756402992</v>
+        <v>3.729092756402999</v>
       </c>
     </row>
     <row r="73">
@@ -3129,19 +3129,19 @@
         <v>0.1287382332705082</v>
       </c>
       <c r="G73" t="n">
-        <v>4.457599970027378</v>
+        <v>4.457599970027377</v>
       </c>
       <c r="H73" t="n">
         <v>0.001</v>
       </c>
       <c r="I73" t="n">
-        <v>535.5348976590852</v>
+        <v>535.5348976590851</v>
       </c>
       <c r="J73" t="n">
         <v>3226.665054744453</v>
       </c>
       <c r="K73" t="n">
-        <v>3.681753471465552</v>
+        <v>3.68175347146555</v>
       </c>
     </row>
     <row r="74">
@@ -3197,25 +3197,25 @@
         <v>128</v>
       </c>
       <c r="E75" t="n">
-        <v>0.1679189404399179</v>
+        <v>0.1679189404399183</v>
       </c>
       <c r="F75" t="n">
-        <v>0.1338172576710621</v>
+        <v>0.1338172576710626</v>
       </c>
       <c r="G75" t="n">
-        <v>4.924066110698617</v>
+        <v>4.924066110698629</v>
       </c>
       <c r="H75" t="n">
         <v>0.001</v>
       </c>
       <c r="I75" t="n">
-        <v>582.7173807094437</v>
+        <v>582.717380709445</v>
       </c>
       <c r="J75" t="n">
         <v>3470.23021454773</v>
       </c>
       <c r="K75" t="n">
-        <v>3.701626443334423</v>
+        <v>3.70162644333443</v>
       </c>
     </row>
     <row r="76">
@@ -3234,25 +3234,25 @@
         <v>132</v>
       </c>
       <c r="E76" t="n">
-        <v>0.1898143693767541</v>
+        <v>0.1898143693767539</v>
       </c>
       <c r="F76" t="n">
-        <v>0.1576641459393237</v>
+        <v>0.1576641459393234</v>
       </c>
       <c r="G76" t="n">
-        <v>5.903982899097546</v>
+        <v>5.903982899097537</v>
       </c>
       <c r="H76" t="n">
         <v>0.001</v>
       </c>
       <c r="I76" t="n">
-        <v>694.32797923934</v>
+        <v>694.3279792393391</v>
       </c>
       <c r="J76" t="n">
         <v>3657.931596639026</v>
       </c>
       <c r="K76" t="n">
-        <v>4.402790676006609</v>
+        <v>4.402790676006603</v>
       </c>
     </row>
     <row r="77">
@@ -3271,25 +3271,25 @@
         <v>137</v>
       </c>
       <c r="E77" t="n">
-        <v>0.1866738930901129</v>
+        <v>0.186673893090113</v>
       </c>
       <c r="F77" t="n">
-        <v>0.1556309119103462</v>
+        <v>0.1556309119103463</v>
       </c>
       <c r="G77" t="n">
-        <v>6.013400968454149</v>
+        <v>6.013400968454151</v>
       </c>
       <c r="H77" t="n">
         <v>0.001</v>
       </c>
       <c r="I77" t="n">
-        <v>703.1646919310973</v>
+        <v>703.1646919310977</v>
       </c>
       <c r="J77" t="n">
         <v>3766.807882405171</v>
       </c>
       <c r="K77" t="n">
-        <v>4.252153723259523</v>
+        <v>4.252153723259525</v>
       </c>
     </row>
     <row r="78">
@@ -3314,19 +3314,19 @@
         <v>0.1566704336469271</v>
       </c>
       <c r="G78" t="n">
-        <v>6.238884541839533</v>
+        <v>6.238884541839532</v>
       </c>
       <c r="H78" t="n">
         <v>0.001</v>
       </c>
       <c r="I78" t="n">
-        <v>724.8835435249122</v>
+        <v>724.8835435249121</v>
       </c>
       <c r="J78" t="n">
         <v>3885.197258525015</v>
       </c>
       <c r="K78" t="n">
-        <v>4.240454106634709</v>
+        <v>4.240454106634712</v>
       </c>
     </row>
     <row r="79">
@@ -3345,25 +3345,25 @@
         <v>146</v>
       </c>
       <c r="E79" t="n">
-        <v>0.1843405653621117</v>
+        <v>0.1843405653621116</v>
       </c>
       <c r="F79" t="n">
-        <v>0.1552098712679014</v>
+        <v>0.1552098712679011</v>
       </c>
       <c r="G79" t="n">
-        <v>6.328052629502888</v>
+        <v>6.328052629502882</v>
       </c>
       <c r="H79" t="n">
         <v>0.001</v>
       </c>
       <c r="I79" t="n">
-        <v>735.4403061166397</v>
+        <v>735.440306116639</v>
       </c>
       <c r="J79" t="n">
         <v>3989.573888264735</v>
       </c>
       <c r="K79" t="n">
-        <v>4.12050358010924</v>
+        <v>4.120503580109239</v>
       </c>
     </row>
     <row r="80">
@@ -3382,25 +3382,25 @@
         <v>151</v>
       </c>
       <c r="E80" t="n">
-        <v>0.196494151644095</v>
+        <v>0.1964941516440948</v>
       </c>
       <c r="F80" t="n">
-        <v>0.1687870534249258</v>
+        <v>0.1687870534249256</v>
       </c>
       <c r="G80" t="n">
-        <v>7.091834377233721</v>
+        <v>7.091834377233714</v>
       </c>
       <c r="H80" t="n">
         <v>0.001</v>
       </c>
       <c r="I80" t="n">
-        <v>826.9751029509093</v>
+        <v>826.9751029509085</v>
       </c>
       <c r="J80" t="n">
         <v>4208.649957423613</v>
       </c>
       <c r="K80" t="n">
-        <v>4.613896777623493</v>
+        <v>4.613896777623492</v>
       </c>
     </row>
     <row r="81">
@@ -3422,22 +3422,22 @@
         <v>0.1909420999615216</v>
       </c>
       <c r="F81" t="n">
-        <v>0.1639735032935723</v>
+        <v>0.1639735032935722</v>
       </c>
       <c r="G81" t="n">
-        <v>7.08016447101402</v>
+        <v>7.080164471014019</v>
       </c>
       <c r="H81" t="n">
         <v>0.001</v>
       </c>
       <c r="I81" t="n">
-        <v>829.6509627524454</v>
+        <v>829.6509627524451</v>
       </c>
       <c r="J81" t="n">
         <v>4345.039480133692</v>
       </c>
       <c r="K81" t="n">
-        <v>4.416299335543786</v>
+        <v>4.416299335543783</v>
       </c>
     </row>
     <row r="82">
@@ -3468,13 +3468,13 @@
         <v>0.001</v>
       </c>
       <c r="I82" t="n">
-        <v>830.7790011658839</v>
+        <v>830.779001165884</v>
       </c>
       <c r="J82" t="n">
         <v>4427.708897652928</v>
       </c>
       <c r="K82" t="n">
-        <v>4.367324964565433</v>
+        <v>4.367324964565431</v>
       </c>
     </row>
     <row r="83">
@@ -3493,25 +3493,25 @@
         <v>165</v>
       </c>
       <c r="E83" t="n">
-        <v>0.1912594112921341</v>
+        <v>0.191259411292134</v>
       </c>
       <c r="F83" t="n">
-        <v>0.16582731730761</v>
+        <v>0.1658273173076099</v>
       </c>
       <c r="G83" t="n">
-        <v>7.520395741244077</v>
+        <v>7.520395741244072</v>
       </c>
       <c r="H83" t="n">
         <v>0.001</v>
       </c>
       <c r="I83" t="n">
-        <v>871.9509590643812</v>
+        <v>871.9509590643808</v>
       </c>
       <c r="J83" t="n">
         <v>4558.996355648836</v>
       </c>
       <c r="K83" t="n">
-        <v>4.470009394257569</v>
+        <v>4.470009394257567</v>
       </c>
     </row>
     <row r="84">
@@ -3530,25 +3530,25 @@
         <v>170</v>
       </c>
       <c r="E84" t="n">
-        <v>0.1977795627045712</v>
+        <v>0.1977795627045713</v>
       </c>
       <c r="F84" t="n">
-        <v>0.1733216225431252</v>
+        <v>0.1733216225431253</v>
       </c>
       <c r="G84" t="n">
-        <v>8.086517564399752</v>
+        <v>8.086517564399758</v>
       </c>
       <c r="H84" t="n">
         <v>0.001</v>
       </c>
       <c r="I84" t="n">
-        <v>928.9421551934223</v>
+        <v>928.9421551934228</v>
       </c>
       <c r="J84" t="n">
         <v>4696.856148787268</v>
       </c>
       <c r="K84" t="n">
-        <v>4.650872677087458</v>
+        <v>4.65087267708746</v>
       </c>
     </row>
     <row r="85">
@@ -3573,19 +3573,19 @@
         <v>0.1773327946567735</v>
       </c>
       <c r="G85" t="n">
-        <v>8.458319300043655</v>
+        <v>8.45831930004365</v>
       </c>
       <c r="H85" t="n">
         <v>0.001</v>
       </c>
       <c r="I85" t="n">
-        <v>963.7787172298437</v>
+        <v>963.7787172298434</v>
       </c>
       <c r="J85" t="n">
         <v>4792.312939005513</v>
       </c>
       <c r="K85" t="n">
-        <v>4.745112312625918</v>
+        <v>4.745112312625917</v>
       </c>
     </row>
     <row r="86">
@@ -3604,25 +3604,25 @@
         <v>179</v>
       </c>
       <c r="E86" t="n">
-        <v>0.1967908023501506</v>
+        <v>0.1967908023501508</v>
       </c>
       <c r="F86" t="n">
-        <v>0.1735766636897502</v>
+        <v>0.1735766636897504</v>
       </c>
       <c r="G86" t="n">
-        <v>8.477195954973997</v>
+        <v>8.477195954974007</v>
       </c>
       <c r="H86" t="n">
         <v>0.001</v>
       </c>
       <c r="I86" t="n">
-        <v>967.3026022796006</v>
+        <v>967.3026022796018</v>
       </c>
       <c r="J86" t="n">
         <v>4915.385224958205</v>
       </c>
       <c r="K86" t="n">
-        <v>4.622249544946809</v>
+        <v>4.622249544946817</v>
       </c>
     </row>
     <row r="87">
@@ -3641,25 +3641,25 @@
         <v>184</v>
       </c>
       <c r="E87" t="n">
-        <v>0.1998056512523499</v>
+        <v>0.1998056512523497</v>
       </c>
       <c r="F87" t="n">
-        <v>0.1773282819055059</v>
+        <v>0.1773282819055056</v>
       </c>
       <c r="G87" t="n">
-        <v>8.889191976569238</v>
+        <v>8.889191976569229</v>
       </c>
       <c r="H87" t="n">
         <v>0.001</v>
       </c>
       <c r="I87" t="n">
-        <v>1003.08029839762</v>
+        <v>1003.080298397619</v>
       </c>
       <c r="J87" t="n">
         <v>5020.279917562256</v>
       </c>
       <c r="K87" t="n">
-        <v>4.709001941985301</v>
+        <v>4.709001941985292</v>
       </c>
     </row>
     <row r="88">
@@ -3678,25 +3678,25 @@
         <v>188</v>
       </c>
       <c r="E88" t="n">
-        <v>0.2003347081567013</v>
+        <v>0.2003347081567015</v>
       </c>
       <c r="F88" t="n">
-        <v>0.1783658814577096</v>
+        <v>0.1783658814577099</v>
       </c>
       <c r="G88" t="n">
-        <v>9.11904449434688</v>
+        <v>9.119044494346888</v>
       </c>
       <c r="H88" t="n">
         <v>0.001</v>
       </c>
       <c r="I88" t="n">
-        <v>1016.21423105763</v>
+        <v>1016.214231057631</v>
       </c>
       <c r="J88" t="n">
         <v>5072.581982462818</v>
       </c>
       <c r="K88" t="n">
-        <v>4.674361523025206</v>
+        <v>4.67436152302521</v>
       </c>
     </row>
     <row r="89">
@@ -3715,25 +3715,25 @@
         <v>193</v>
       </c>
       <c r="E89" t="n">
-        <v>0.2004832439013848</v>
+        <v>0.2004832439013847</v>
       </c>
       <c r="F89" t="n">
-        <v>0.1791057905297641</v>
+        <v>0.1791057905297638</v>
       </c>
       <c r="G89" t="n">
-        <v>9.378256634044767</v>
+        <v>9.378256634044764</v>
       </c>
       <c r="H89" t="n">
         <v>0.001</v>
       </c>
       <c r="I89" t="n">
-        <v>1035.149830666143</v>
+        <v>1035.149830666142</v>
       </c>
       <c r="J89" t="n">
         <v>5163.273551057066</v>
       </c>
       <c r="K89" t="n">
-        <v>4.631984768158491</v>
+        <v>4.631984768158489</v>
       </c>
     </row>
     <row r="90">
@@ -3752,25 +3752,25 @@
         <v>198</v>
       </c>
       <c r="E90" t="n">
-        <v>0.1966770500476557</v>
+        <v>0.196677050047656</v>
       </c>
       <c r="F90" t="n">
-        <v>0.1757571815593134</v>
+        <v>0.1757571815593136</v>
       </c>
       <c r="G90" t="n">
-        <v>9.401447726942214</v>
+        <v>9.401447726942227</v>
       </c>
       <c r="H90" t="n">
         <v>0.001</v>
       </c>
       <c r="I90" t="n">
-        <v>1044.160908794896</v>
+        <v>1044.160908794897</v>
       </c>
       <c r="J90" t="n">
         <v>5309.012457436651</v>
       </c>
       <c r="K90" t="n">
-        <v>4.565004657665559</v>
+        <v>4.565004657665564</v>
       </c>
     </row>
     <row r="91">
@@ -3789,25 +3789,25 @@
         <v>202</v>
       </c>
       <c r="E91" t="n">
-        <v>0.1910186752401951</v>
+        <v>0.1910186752401954</v>
       </c>
       <c r="F91" t="n">
-        <v>0.170381396547343</v>
+        <v>0.1703813965473432</v>
       </c>
       <c r="G91" t="n">
-        <v>9.256001146428064</v>
+        <v>9.256001146428074</v>
       </c>
       <c r="H91" t="n">
         <v>0.001</v>
       </c>
       <c r="I91" t="n">
-        <v>1033.546991268666</v>
+        <v>1033.546991268668</v>
       </c>
       <c r="J91" t="n">
         <v>5410.711753544724</v>
       </c>
       <c r="K91" t="n">
-        <v>4.412718370940306</v>
+        <v>4.412718370940309</v>
       </c>
     </row>
     <row r="92">
@@ -3826,25 +3826,25 @@
         <v>207</v>
       </c>
       <c r="E92" t="n">
-        <v>0.189965134535225</v>
+        <v>0.1899651345352254</v>
       </c>
       <c r="F92" t="n">
-        <v>0.1698150135037628</v>
+        <v>0.1698150135037633</v>
       </c>
       <c r="G92" t="n">
-        <v>9.427493474536282</v>
+        <v>9.427493474536309</v>
       </c>
       <c r="H92" t="n">
         <v>0.001</v>
       </c>
       <c r="I92" t="n">
-        <v>1060.365810237204</v>
+        <v>1060.365810237207</v>
       </c>
       <c r="J92" t="n">
         <v>5581.896977208637</v>
       </c>
       <c r="K92" t="n">
-        <v>4.482980887075852</v>
+        <v>4.482980887075862</v>
       </c>
     </row>
     <row r="93">
@@ -3863,25 +3863,25 @@
         <v>212</v>
       </c>
       <c r="E93" t="n">
-        <v>0.1944542017511583</v>
+        <v>0.194454201751158</v>
       </c>
       <c r="F93" t="n">
-        <v>0.1749021192693904</v>
+        <v>0.17490211926939</v>
       </c>
       <c r="G93" t="n">
-        <v>9.945447086390086</v>
+        <v>9.945447086390073</v>
       </c>
       <c r="H93" t="n">
         <v>0.001</v>
       </c>
       <c r="I93" t="n">
-        <v>1109.347921704105</v>
+        <v>1109.347921704103</v>
       </c>
       <c r="J93" t="n">
         <v>5704.931607102682</v>
       </c>
       <c r="K93" t="n">
-        <v>4.60419777221746</v>
+        <v>4.604197772217451</v>
       </c>
     </row>
     <row r="94">
@@ -3900,25 +3900,25 @@
         <v>216</v>
       </c>
       <c r="E94" t="n">
-        <v>0.1870785774178997</v>
+        <v>0.1870785774179001</v>
       </c>
       <c r="F94" t="n">
-        <v>0.1677233054516593</v>
+        <v>0.1677233054516597</v>
       </c>
       <c r="G94" t="n">
-        <v>9.665510138230179</v>
+        <v>9.6655101382302</v>
       </c>
       <c r="H94" t="n">
         <v>0.001</v>
       </c>
       <c r="I94" t="n">
-        <v>1075.328205134727</v>
+        <v>1075.32820513473</v>
       </c>
       <c r="J94" t="n">
         <v>5748.002897908714</v>
       </c>
       <c r="K94" t="n">
-        <v>4.388162878357392</v>
+        <v>4.388162878357402</v>
       </c>
     </row>
     <row r="95">
@@ -3937,13 +3937,13 @@
         <v>221</v>
       </c>
       <c r="E95" t="n">
-        <v>0.1874142986462785</v>
+        <v>0.1874142986462784</v>
       </c>
       <c r="F95" t="n">
-        <v>0.1685169567543314</v>
+        <v>0.1685169567543313</v>
       </c>
       <c r="G95" t="n">
-        <v>9.917495260333091</v>
+        <v>9.917495260333087</v>
       </c>
       <c r="H95" t="n">
         <v>0.001</v>
@@ -3955,7 +3955,7 @@
         <v>5864.345167020192</v>
       </c>
       <c r="K95" t="n">
-        <v>4.402013526601421</v>
+        <v>4.402013526601426</v>
       </c>
     </row>
     <row r="96">
@@ -3974,25 +3974,25 @@
         <v>226</v>
       </c>
       <c r="E96" t="n">
-        <v>0.1854214466450856</v>
+        <v>0.1854214466450859</v>
       </c>
       <c r="F96" t="n">
-        <v>0.1669082977052011</v>
+        <v>0.1669082977052015</v>
       </c>
       <c r="G96" t="n">
-        <v>10.01566223267489</v>
+        <v>10.01566223267491</v>
       </c>
       <c r="H96" t="n">
         <v>0.001</v>
       </c>
       <c r="I96" t="n">
-        <v>1103.682521513987</v>
+        <v>1103.682521513989</v>
       </c>
       <c r="J96" t="n">
         <v>5952.291611803357</v>
       </c>
       <c r="K96" t="n">
-        <v>4.298214931583267</v>
+        <v>4.298214931583275</v>
       </c>
     </row>
     <row r="97">
@@ -4017,7 +4017,7 @@
         <v>0.1676857096888021</v>
       </c>
       <c r="G97" t="n">
-        <v>10.34817174249319</v>
+        <v>10.3481717424932</v>
       </c>
       <c r="H97" t="n">
         <v>0.001</v>
@@ -4029,7 +4029,7 @@
         <v>6120.49474534301</v>
       </c>
       <c r="K97" t="n">
-        <v>4.30934533691014</v>
+        <v>4.309345336910141</v>
       </c>
     </row>
   </sheetData>

--- a/results/ref_threshold_sensitivity/tables/threshold_comparison_summary.xlsx
+++ b/results/ref_threshold_sensitivity/tables/threshold_comparison_summary.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -496,25 +496,25 @@
         <v>11</v>
       </c>
       <c r="E2" t="n">
-        <v>0.5755852889762161</v>
+        <v>0.6443202593770726</v>
       </c>
       <c r="F2" t="n">
-        <v>0.1511705779524322</v>
+        <v>0.2886405187541452</v>
       </c>
       <c r="G2" t="n">
-        <v>1.356185999273623</v>
+        <v>1.811518019689926</v>
       </c>
       <c r="H2" t="n">
-        <v>0.199</v>
+        <v>0.08</v>
       </c>
       <c r="I2" t="n">
-        <v>190.6934098998242</v>
+        <v>165.1808619198125</v>
       </c>
       <c r="J2" t="n">
-        <v>331.3034810861955</v>
+        <v>256.3645322583974</v>
       </c>
       <c r="K2" t="n">
-        <v>8.294327430324556</v>
+        <v>9.68012474643608</v>
       </c>
     </row>
     <row r="3">
@@ -533,25 +533,25 @@
         <v>16</v>
       </c>
       <c r="E3" t="n">
-        <v>0.5256219687263333</v>
+        <v>0.4689109939172542</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2884329530894999</v>
+        <v>0.2033664908758813</v>
       </c>
       <c r="G3" t="n">
-        <v>2.216046840597066</v>
+        <v>1.765847112429949</v>
       </c>
       <c r="H3" t="n">
-        <v>0.005</v>
+        <v>0.075</v>
       </c>
       <c r="I3" t="n">
-        <v>254.084670705896</v>
+        <v>158.6504411884297</v>
       </c>
       <c r="J3" t="n">
-        <v>483.3981184644624</v>
+        <v>338.33807107629</v>
       </c>
       <c r="K3" t="n">
-        <v>10.25014890180994</v>
+        <v>5.58995651403557</v>
       </c>
     </row>
     <row r="4">
@@ -570,25 +570,25 @@
         <v>20</v>
       </c>
       <c r="E4" t="n">
-        <v>0.4240549598658218</v>
+        <v>0.3666652359844062</v>
       </c>
       <c r="F4" t="n">
-        <v>0.2183603026750438</v>
+        <v>0.1404742488359799</v>
       </c>
       <c r="G4" t="n">
-        <v>2.061574985258458</v>
+        <v>1.621042644567446</v>
       </c>
       <c r="H4" t="n">
-        <v>0.004</v>
+        <v>0.043</v>
       </c>
       <c r="I4" t="n">
-        <v>262.0799181803198</v>
+        <v>142.1628684792252</v>
       </c>
       <c r="J4" t="n">
-        <v>618.0329037142883</v>
+        <v>387.7184268575468</v>
       </c>
       <c r="K4" t="n">
-        <v>8.532316708043751</v>
+        <v>4.456151476143524</v>
       </c>
     </row>
     <row r="5">
@@ -607,25 +607,25 @@
         <v>25</v>
       </c>
       <c r="E5" t="n">
-        <v>0.3430968682153296</v>
+        <v>0.2911324999107305</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1702276230088375</v>
+        <v>0.1045884209398702</v>
       </c>
       <c r="G5" t="n">
-        <v>1.98471895799337</v>
+        <v>1.560663310874679</v>
       </c>
       <c r="H5" t="n">
-        <v>0.01</v>
+        <v>0.077</v>
       </c>
       <c r="I5" t="n">
-        <v>248.3873571825597</v>
+        <v>136.9683826522153</v>
       </c>
       <c r="J5" t="n">
-        <v>723.9569351786397</v>
+        <v>470.4675111648947</v>
       </c>
       <c r="K5" t="n">
-        <v>6.183664494146682</v>
+        <v>3.415751845326127</v>
       </c>
     </row>
     <row r="6">
@@ -644,25 +644,25 @@
         <v>30</v>
       </c>
       <c r="E6" t="n">
-        <v>0.3405615461937538</v>
+        <v>0.2246349589696992</v>
       </c>
       <c r="F6" t="n">
-        <v>0.2031785349841192</v>
+        <v>0.06310057542171998</v>
       </c>
       <c r="G6" t="n">
-        <v>2.478920378838445</v>
+        <v>1.390632471154215</v>
       </c>
       <c r="H6" t="n">
-        <v>0.001</v>
+        <v>0.104</v>
       </c>
       <c r="I6" t="n">
-        <v>311.3986155603586</v>
+        <v>129.4979637321855</v>
       </c>
       <c r="J6" t="n">
-        <v>914.3681047982918</v>
+        <v>576.4817921757822</v>
       </c>
       <c r="K6" t="n">
-        <v>7.388694435646975</v>
+        <v>2.071876596765784</v>
       </c>
     </row>
     <row r="7">
@@ -681,25 +681,25 @@
         <v>34</v>
       </c>
       <c r="E7" t="n">
-        <v>0.2817620862995145</v>
+        <v>0.1955137158814499</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1535053159958564</v>
+        <v>0.05185545086028032</v>
       </c>
       <c r="G7" t="n">
-        <v>2.196859359801594</v>
+        <v>1.360963922630131</v>
       </c>
       <c r="H7" t="n">
-        <v>0.001</v>
+        <v>0.103</v>
       </c>
       <c r="I7" t="n">
-        <v>290.3417616227973</v>
+        <v>125.5456396122126</v>
       </c>
       <c r="J7" t="n">
-        <v>1030.450070255948</v>
+        <v>642.132134035739</v>
       </c>
       <c r="K7" t="n">
-        <v>5.828707214872598</v>
+        <v>1.709419770825983</v>
       </c>
     </row>
     <row r="8">
@@ -718,25 +718,25 @@
         <v>39</v>
       </c>
       <c r="E8" t="n">
-        <v>0.2551292489076619</v>
+        <v>0.2186339985917645</v>
       </c>
       <c r="F8" t="n">
-        <v>0.1422700441967016</v>
+        <v>0.1002452104996076</v>
       </c>
       <c r="G8" t="n">
-        <v>2.260597614178341</v>
+        <v>1.846745811956231</v>
       </c>
       <c r="H8" t="n">
-        <v>0.001</v>
+        <v>0.003</v>
       </c>
       <c r="I8" t="n">
-        <v>296.5920555245094</v>
+        <v>174.173133480673</v>
       </c>
       <c r="J8" t="n">
-        <v>1162.51686858473</v>
+        <v>796.6424920302114</v>
       </c>
       <c r="K8" t="n">
-        <v>5.705509415246414</v>
+        <v>2.129642101991388</v>
       </c>
     </row>
     <row r="9">
@@ -755,25 +755,25 @@
         <v>44</v>
       </c>
       <c r="E9" t="n">
-        <v>0.2600434908304277</v>
+        <v>0.1985267928438633</v>
       </c>
       <c r="F9" t="n">
-        <v>0.1626807922554839</v>
+        <v>0.09306979190226639</v>
       </c>
       <c r="G9" t="n">
-        <v>2.670873903831481</v>
+        <v>1.882537821778274</v>
       </c>
       <c r="H9" t="n">
-        <v>0.001</v>
+        <v>0.004</v>
       </c>
       <c r="I9" t="n">
-        <v>340.5974270481969</v>
+        <v>187.8682664424388</v>
       </c>
       <c r="J9" t="n">
-        <v>1309.77101545794</v>
+        <v>946.3118995237725</v>
       </c>
       <c r="K9" t="n">
-        <v>6.079869406982926</v>
+        <v>1.980510461400006</v>
       </c>
     </row>
     <row r="10">
@@ -792,25 +792,25 @@
         <v>48</v>
       </c>
       <c r="E10" t="n">
-        <v>0.2958595079622763</v>
+        <v>0.2409467313386454</v>
       </c>
       <c r="F10" t="n">
-        <v>0.2120332589101663</v>
+        <v>0.1505832469741984</v>
       </c>
       <c r="G10" t="n">
-        <v>3.529437512805296</v>
+        <v>2.666417004980438</v>
       </c>
       <c r="H10" t="n">
         <v>0.001</v>
       </c>
       <c r="I10" t="n">
-        <v>436.2145161079192</v>
+        <v>275.667364815095</v>
       </c>
       <c r="J10" t="n">
-        <v>1474.397490593876</v>
+        <v>1144.100869447573</v>
       </c>
       <c r="K10" t="n">
-        <v>7.515089085891455</v>
+        <v>3.567624563745578</v>
       </c>
     </row>
     <row r="11">
@@ -829,25 +829,25 @@
         <v>53</v>
       </c>
       <c r="E11" t="n">
-        <v>0.286061195857017</v>
+        <v>0.2042706702842212</v>
       </c>
       <c r="F11" t="n">
-        <v>0.2101102592460613</v>
+        <v>0.1196186139314788</v>
       </c>
       <c r="G11" t="n">
-        <v>3.766394578151311</v>
+        <v>2.413062116684228</v>
       </c>
       <c r="H11" t="n">
         <v>0.001</v>
       </c>
       <c r="I11" t="n">
-        <v>448.2318414853746</v>
+        <v>250.1224457054725</v>
       </c>
       <c r="J11" t="n">
-        <v>1566.908927100395</v>
+        <v>1224.465780415041</v>
       </c>
       <c r="K11" t="n">
-        <v>7.188244463959986</v>
+        <v>2.871520683989147</v>
       </c>
     </row>
     <row r="12">
@@ -866,25 +866,25 @@
         <v>58</v>
       </c>
       <c r="E12" t="n">
-        <v>0.2893160670625263</v>
+        <v>0.1921852214151583</v>
       </c>
       <c r="F12" t="n">
-        <v>0.2209810735108461</v>
+        <v>0.114510723474308</v>
       </c>
       <c r="G12" t="n">
-        <v>4.233790800663843</v>
+        <v>2.474238347333883</v>
       </c>
       <c r="H12" t="n">
         <v>0.001</v>
       </c>
       <c r="I12" t="n">
-        <v>498.1335897537953</v>
+        <v>253.0112899163396</v>
       </c>
       <c r="J12" t="n">
-        <v>1721.762620415201</v>
+        <v>1316.497116965019</v>
       </c>
       <c r="K12" t="n">
-        <v>7.394514241080915</v>
+        <v>2.556795948137522</v>
       </c>
     </row>
     <row r="13">
@@ -903,25 +903,25 @@
         <v>62</v>
       </c>
       <c r="E13" t="n">
-        <v>0.2794460989117291</v>
+        <v>0.1777104481883768</v>
       </c>
       <c r="F13" t="n">
-        <v>0.215110929171705</v>
+        <v>0.1042917382051962</v>
       </c>
       <c r="G13" t="n">
-        <v>4.343597755954629</v>
+        <v>2.420506274614307</v>
       </c>
       <c r="H13" t="n">
         <v>0.001</v>
       </c>
       <c r="I13" t="n">
-        <v>506.888973313834</v>
+        <v>247.1104432080927</v>
       </c>
       <c r="J13" t="n">
-        <v>1813.906063773498</v>
+        <v>1390.52287430028</v>
       </c>
       <c r="K13" t="n">
-        <v>7.070405377868595</v>
+        <v>2.410577506300852</v>
       </c>
     </row>
     <row r="14">
@@ -940,25 +940,25 @@
         <v>67</v>
       </c>
       <c r="E14" t="n">
-        <v>0.2662099333705263</v>
+        <v>0.1521801414972533</v>
       </c>
       <c r="F14" t="n">
-        <v>0.2060632065976186</v>
+        <v>0.08268671047243781</v>
       </c>
       <c r="G14" t="n">
-        <v>4.426008656724394</v>
+        <v>2.189849303064508</v>
       </c>
       <c r="H14" t="n">
-        <v>0.001</v>
+        <v>0.002</v>
       </c>
       <c r="I14" t="n">
-        <v>520.0013463685008</v>
+        <v>221.5673143028797</v>
       </c>
       <c r="J14" t="n">
-        <v>1953.350649935113</v>
+        <v>1455.954187734008</v>
       </c>
       <c r="K14" t="n">
-        <v>6.638738296098114</v>
+        <v>1.975799641944416</v>
       </c>
     </row>
     <row r="15">
@@ -977,25 +977,25 @@
         <v>72</v>
       </c>
       <c r="E15" t="n">
-        <v>0.2346826155705918</v>
+        <v>0.1336576952556855</v>
       </c>
       <c r="F15" t="n">
-        <v>0.1767040258410912</v>
+        <v>0.06802570247202533</v>
       </c>
       <c r="G15" t="n">
-        <v>4.047746188127459</v>
+        <v>2.036471689900616</v>
       </c>
       <c r="H15" t="n">
         <v>0.001</v>
       </c>
       <c r="I15" t="n">
-        <v>486.4548087603538</v>
+        <v>208.0440210742577</v>
       </c>
       <c r="J15" t="n">
-        <v>2072.819955485922</v>
+        <v>1556.54353216455</v>
       </c>
       <c r="K15" t="n">
-        <v>5.839829976999286</v>
+        <v>1.41531315510678</v>
       </c>
     </row>
     <row r="16">
@@ -1014,25 +1014,25 @@
         <v>76</v>
       </c>
       <c r="E16" t="n">
-        <v>0.2323611456709234</v>
+        <v>0.1350383082764846</v>
       </c>
       <c r="F16" t="n">
-        <v>0.1775297989331323</v>
+        <v>0.07325533029623343</v>
       </c>
       <c r="G16" t="n">
-        <v>4.237742814928419</v>
+        <v>2.185687914228568</v>
       </c>
       <c r="H16" t="n">
         <v>0.001</v>
       </c>
       <c r="I16" t="n">
-        <v>496.2224308025017</v>
+        <v>226.4931404417058</v>
       </c>
       <c r="J16" t="n">
-        <v>2135.565433582714</v>
+        <v>1677.251021080416</v>
       </c>
       <c r="K16" t="n">
-        <v>5.669571852455072</v>
+        <v>1.633616555137149</v>
       </c>
     </row>
     <row r="17">
@@ -1051,25 +1051,25 @@
         <v>81</v>
       </c>
       <c r="E17" t="n">
-        <v>0.2324913222434055</v>
+        <v>0.1319761409598392</v>
       </c>
       <c r="F17" t="n">
-        <v>0.1813240770596326</v>
+        <v>0.07410788369049515</v>
       </c>
       <c r="G17" t="n">
-        <v>4.543752969470733</v>
+        <v>2.280630991625768</v>
       </c>
       <c r="H17" t="n">
         <v>0.001</v>
       </c>
       <c r="I17" t="n">
-        <v>525.9191440067971</v>
+        <v>231.5695869645354</v>
       </c>
       <c r="J17" t="n">
-        <v>2262.102253675468</v>
+        <v>1754.632203066181</v>
       </c>
       <c r="K17" t="n">
-        <v>5.725451480651319</v>
+        <v>1.555795937951935</v>
       </c>
     </row>
     <row r="18">
@@ -1088,25 +1088,25 @@
         <v>86</v>
       </c>
       <c r="E18" t="n">
-        <v>0.2329768550408528</v>
+        <v>0.1310199780786279</v>
       </c>
       <c r="F18" t="n">
-        <v>0.1850379084809062</v>
+        <v>0.07670872670854212</v>
       </c>
       <c r="G18" t="n">
-        <v>4.859865970344588</v>
+        <v>2.412391075024884</v>
       </c>
       <c r="H18" t="n">
         <v>0.001</v>
       </c>
       <c r="I18" t="n">
-        <v>545.9729369709584</v>
+        <v>246.7061984752153</v>
       </c>
       <c r="J18" t="n">
-        <v>2343.464276205554</v>
+        <v>1882.966262802774</v>
       </c>
       <c r="K18" t="n">
-        <v>5.564041607145979</v>
+        <v>1.685940351533008</v>
       </c>
     </row>
     <row r="19">
@@ -1125,25 +1125,25 @@
         <v>90</v>
       </c>
       <c r="E19" t="n">
-        <v>0.2224747594224215</v>
+        <v>0.1369750378595389</v>
       </c>
       <c r="F19" t="n">
-        <v>0.1761934951023275</v>
+        <v>0.08560450439879719</v>
       </c>
       <c r="G19" t="n">
-        <v>4.807015596715873</v>
+        <v>2.666412603330615</v>
       </c>
       <c r="H19" t="n">
         <v>0.001</v>
       </c>
       <c r="I19" t="n">
-        <v>550.5707756198968</v>
+        <v>274.3252213555073</v>
       </c>
       <c r="J19" t="n">
-        <v>2474.756134355478</v>
+        <v>2002.738788339042</v>
       </c>
       <c r="K19" t="n">
-        <v>5.24615075865755</v>
+        <v>1.891149717524331</v>
       </c>
     </row>
     <row r="20">
@@ -1162,25 +1162,25 @@
         <v>95</v>
       </c>
       <c r="E20" t="n">
-        <v>0.2279835395489326</v>
+        <v>0.1466880592492044</v>
       </c>
       <c r="F20" t="n">
-        <v>0.1846118282876367</v>
+        <v>0.09874918617331707</v>
       </c>
       <c r="G20" t="n">
-        <v>5.256503211861522</v>
+        <v>3.059897945806875</v>
       </c>
       <c r="H20" t="n">
         <v>0.001</v>
       </c>
       <c r="I20" t="n">
-        <v>591.9513970181738</v>
+        <v>323.223850557419</v>
       </c>
       <c r="J20" t="n">
-        <v>2596.465508822938</v>
+        <v>2203.477585099839</v>
       </c>
       <c r="K20" t="n">
-        <v>5.353943655071093</v>
+        <v>2.185895472559385</v>
       </c>
     </row>
     <row r="21">
@@ -1199,25 +1199,25 @@
         <v>100</v>
       </c>
       <c r="E21" t="n">
-        <v>0.2141315808957047</v>
+        <v>0.1567278246711239</v>
       </c>
       <c r="F21" t="n">
-        <v>0.172330069241221</v>
+        <v>0.1118729217280986</v>
       </c>
       <c r="G21" t="n">
-        <v>5.1225798403091</v>
+        <v>3.494106873226311</v>
       </c>
       <c r="H21" t="n">
         <v>0.001</v>
       </c>
       <c r="I21" t="n">
-        <v>584.9491316892047</v>
+        <v>380.413557026489</v>
       </c>
       <c r="J21" t="n">
-        <v>2731.727516522241</v>
+        <v>2427.224124527633</v>
       </c>
       <c r="K21" t="n">
-        <v>4.985494666598618</v>
+        <v>2.727766722989574</v>
       </c>
     </row>
     <row r="22">
@@ -1236,25 +1236,25 @@
         <v>104</v>
       </c>
       <c r="E22" t="n">
-        <v>0.2232963412792219</v>
+        <v>0.1676838342009694</v>
       </c>
       <c r="F22" t="n">
-        <v>0.1836686035893864</v>
+        <v>0.1252187237010189</v>
       </c>
       <c r="G22" t="n">
-        <v>5.634849585079812</v>
+        <v>3.948743620981858</v>
       </c>
       <c r="H22" t="n">
         <v>0.001</v>
       </c>
       <c r="I22" t="n">
-        <v>635.678056637066</v>
+        <v>427.3427058190591</v>
       </c>
       <c r="J22" t="n">
-        <v>2846.791187868947</v>
+        <v>2548.502709610564</v>
       </c>
       <c r="K22" t="n">
-        <v>5.342279290739274</v>
+        <v>3.142273567068756</v>
       </c>
     </row>
     <row r="23">
@@ -1273,25 +1273,25 @@
         <v>109</v>
       </c>
       <c r="E23" t="n">
-        <v>0.2185174809382151</v>
+        <v>0.1553402395353086</v>
       </c>
       <c r="F23" t="n">
-        <v>0.1805814363235654</v>
+        <v>0.114337338541877</v>
       </c>
       <c r="G23" t="n">
-        <v>5.760154574834885</v>
+        <v>3.788518269968095</v>
       </c>
       <c r="H23" t="n">
         <v>0.001</v>
       </c>
       <c r="I23" t="n">
-        <v>655.3893111570943</v>
+        <v>413.7535447079672</v>
       </c>
       <c r="J23" t="n">
-        <v>2999.253461751203</v>
+        <v>2663.531007456194</v>
       </c>
       <c r="K23" t="n">
-        <v>5.299448413396805</v>
+        <v>2.882354577134603</v>
       </c>
     </row>
     <row r="24">
@@ -1310,25 +1310,25 @@
         <v>114</v>
       </c>
       <c r="E24" t="n">
-        <v>0.220858236645828</v>
+        <v>0.1541046092455618</v>
       </c>
       <c r="F24" t="n">
-        <v>0.1847868587127646</v>
+        <v>0.114942785599523</v>
       </c>
       <c r="G24" t="n">
-        <v>6.122811195504295</v>
+        <v>3.935072345926091</v>
       </c>
       <c r="H24" t="n">
         <v>0.001</v>
       </c>
       <c r="I24" t="n">
-        <v>705.6293275768203</v>
+        <v>422.8410738954885</v>
       </c>
       <c r="J24" t="n">
-        <v>3194.942322700781</v>
+        <v>2743.857409363415</v>
       </c>
       <c r="K24" t="n">
-        <v>5.398015944144066</v>
+        <v>2.846123390401187</v>
       </c>
     </row>
     <row r="25">
@@ -1347,25 +1347,25 @@
         <v>118</v>
       </c>
       <c r="E25" t="n">
-        <v>0.2061241458806003</v>
+        <v>0.1522261841554092</v>
       </c>
       <c r="F25" t="n">
-        <v>0.1706832595359842</v>
+        <v>0.1143791388052041</v>
       </c>
       <c r="G25" t="n">
-        <v>5.815998614603307</v>
+        <v>4.022141827633709</v>
       </c>
       <c r="H25" t="n">
         <v>0.001</v>
       </c>
       <c r="I25" t="n">
-        <v>678.8132858778257</v>
+        <v>434.1694188203772</v>
       </c>
       <c r="J25" t="n">
-        <v>3293.225463605006</v>
+        <v>2852.133627531053</v>
       </c>
       <c r="K25" t="n">
-        <v>4.960461723362688</v>
+        <v>2.907770016140893</v>
       </c>
     </row>
     <row r="26">
@@ -1384,25 +1384,25 @@
         <v>123</v>
       </c>
       <c r="E26" t="n">
-        <v>0.2031645653783599</v>
+        <v>0.1547169841265005</v>
       </c>
       <c r="F26" t="n">
-        <v>0.1691117690270078</v>
+        <v>0.1185937783199408</v>
       </c>
       <c r="G26" t="n">
-        <v>5.966163932093431</v>
+        <v>4.283035812353194</v>
       </c>
       <c r="H26" t="n">
         <v>0.001</v>
       </c>
       <c r="I26" t="n">
-        <v>689.9503162673107</v>
+        <v>471.4786403214896</v>
       </c>
       <c r="J26" t="n">
-        <v>3396.016992345067</v>
+        <v>3047.361884562051</v>
       </c>
       <c r="K26" t="n">
-        <v>4.853376658121173</v>
+        <v>3.028543115037929</v>
       </c>
     </row>
     <row r="27">
@@ -1421,25 +1421,25 @@
         <v>128</v>
       </c>
       <c r="E27" t="n">
-        <v>0.1918685918658001</v>
+        <v>0.1493817852781252</v>
       </c>
       <c r="F27" t="n">
-        <v>0.158748452188169</v>
+        <v>0.1145203830354254</v>
       </c>
       <c r="G27" t="n">
-        <v>5.793109380978406</v>
+        <v>4.285019410239204</v>
       </c>
       <c r="H27" t="n">
         <v>0.001</v>
       </c>
       <c r="I27" t="n">
-        <v>676.0836276193372</v>
+        <v>471.694216216854</v>
       </c>
       <c r="J27" t="n">
-        <v>3523.680562018274</v>
+        <v>3157.642113719784</v>
       </c>
       <c r="K27" t="n">
-        <v>4.492789531176012</v>
+        <v>2.930842958724122</v>
       </c>
     </row>
     <row r="28">
@@ -1458,25 +1458,25 @@
         <v>132</v>
       </c>
       <c r="E28" t="n">
-        <v>0.1912461827455567</v>
+        <v>0.1484273234033903</v>
       </c>
       <c r="F28" t="n">
-        <v>0.1591527772989517</v>
+        <v>0.1146347568717788</v>
       </c>
       <c r="G28" t="n">
-        <v>5.959049221614723</v>
+        <v>4.392306907631384</v>
       </c>
       <c r="H28" t="n">
         <v>0.001</v>
       </c>
       <c r="I28" t="n">
-        <v>697.0485726523991</v>
+        <v>482.9139844610169</v>
       </c>
       <c r="J28" t="n">
-        <v>3644.77116690892</v>
+        <v>3253.538320222693</v>
       </c>
       <c r="K28" t="n">
-        <v>4.51205329740503</v>
+        <v>2.904762257520165</v>
       </c>
     </row>
     <row r="29">
@@ -1495,25 +1495,25 @@
         <v>137</v>
       </c>
       <c r="E29" t="n">
-        <v>0.1837642497820643</v>
+        <v>0.1376309138251438</v>
       </c>
       <c r="F29" t="n">
-        <v>0.1526102135142043</v>
+        <v>0.1047160632077828</v>
       </c>
       <c r="G29" t="n">
-        <v>5.898569552980956</v>
+        <v>4.181423012521599</v>
       </c>
       <c r="H29" t="n">
         <v>0.001</v>
       </c>
       <c r="I29" t="n">
-        <v>692.1452534146139</v>
+        <v>465.1358431524944</v>
       </c>
       <c r="J29" t="n">
-        <v>3766.484799058931</v>
+        <v>3379.588424032675</v>
       </c>
       <c r="K29" t="n">
-        <v>4.283247081278818</v>
+        <v>2.61336349566819</v>
       </c>
     </row>
     <row r="30">
@@ -1532,25 +1532,25 @@
         <v>142</v>
       </c>
       <c r="E30" t="n">
-        <v>0.1788636025916064</v>
+        <v>0.1417671268639166</v>
       </c>
       <c r="F30" t="n">
-        <v>0.1486747644515919</v>
+        <v>0.1102144477045017</v>
       </c>
       <c r="G30" t="n">
-        <v>5.924825651190848</v>
+        <v>4.493029772453269</v>
       </c>
       <c r="H30" t="n">
         <v>0.001</v>
       </c>
       <c r="I30" t="n">
-        <v>690.6982062168773</v>
+        <v>498.0211495626916</v>
       </c>
       <c r="J30" t="n">
-        <v>3861.591716867779</v>
+        <v>3512.952266012599</v>
       </c>
       <c r="K30" t="n">
-        <v>4.088189128688915</v>
+        <v>2.781984303448982</v>
       </c>
     </row>
     <row r="31">
@@ -1569,25 +1569,25 @@
         <v>146</v>
       </c>
       <c r="E31" t="n">
-        <v>0.1742823078008453</v>
+        <v>0.1394167525559828</v>
       </c>
       <c r="F31" t="n">
-        <v>0.1447923902223039</v>
+        <v>0.1086816365758393</v>
       </c>
       <c r="G31" t="n">
-        <v>5.909894706781558</v>
+        <v>4.53607374203675</v>
       </c>
       <c r="H31" t="n">
         <v>0.001</v>
       </c>
       <c r="I31" t="n">
-        <v>695.2930456525422</v>
+        <v>499.6936543517871</v>
       </c>
       <c r="J31" t="n">
-        <v>3989.464303210069</v>
+        <v>3584.172240356373</v>
       </c>
       <c r="K31" t="n">
-        <v>3.948111421122626</v>
+        <v>2.715299503723694</v>
       </c>
     </row>
     <row r="32">
@@ -1606,25 +1606,25 @@
         <v>151</v>
       </c>
       <c r="E32" t="n">
-        <v>0.170914493351624</v>
+        <v>0.1364507801322241</v>
       </c>
       <c r="F32" t="n">
-        <v>0.1423253379499558</v>
+        <v>0.1066732208264387</v>
       </c>
       <c r="G32" t="n">
-        <v>5.97829809766438</v>
+        <v>4.58233593730812</v>
       </c>
       <c r="H32" t="n">
         <v>0.001</v>
       </c>
       <c r="I32" t="n">
-        <v>704.2853859298879</v>
+        <v>508.4682413583382</v>
       </c>
       <c r="J32" t="n">
-        <v>4120.688492350118</v>
+        <v>3726.385740452491</v>
       </c>
       <c r="K32" t="n">
-        <v>3.857194469720433</v>
+        <v>2.671107622734316</v>
       </c>
     </row>
     <row r="33">
@@ -1643,25 +1643,25 @@
         <v>156</v>
       </c>
       <c r="E33" t="n">
-        <v>0.1659421902880719</v>
+        <v>0.1370440693141079</v>
       </c>
       <c r="F33" t="n">
-        <v>0.1381402632976741</v>
+        <v>0.1082788716245781</v>
       </c>
       <c r="G33" t="n">
-        <v>5.968729805865116</v>
+        <v>4.76423179125206</v>
       </c>
       <c r="H33" t="n">
         <v>0.001</v>
       </c>
       <c r="I33" t="n">
-        <v>704.1443420415294</v>
+        <v>521.0601225137525</v>
       </c>
       <c r="J33" t="n">
-        <v>4243.311124308717</v>
+        <v>3802.135511019246</v>
       </c>
       <c r="K33" t="n">
-        <v>3.704027719384889</v>
+        <v>2.672412769473156</v>
       </c>
     </row>
     <row r="34">
@@ -1680,25 +1680,25 @@
         <v>160</v>
       </c>
       <c r="E34" t="n">
-        <v>0.1626770151973615</v>
+        <v>0.138609563908845</v>
       </c>
       <c r="F34" t="n">
-        <v>0.1354912040024705</v>
+        <v>0.1106423419578334</v>
       </c>
       <c r="G34" t="n">
-        <v>5.983894099431325</v>
+        <v>4.956143450773869</v>
       </c>
       <c r="H34" t="n">
         <v>0.001</v>
       </c>
       <c r="I34" t="n">
-        <v>703.0416022242492</v>
+        <v>549.6988678489253</v>
       </c>
       <c r="J34" t="n">
-        <v>4321.702124736625</v>
+        <v>3965.807642324224</v>
       </c>
       <c r="K34" t="n">
-        <v>3.578043486341034</v>
+        <v>2.775446544737478</v>
       </c>
     </row>
     <row r="35">
@@ -1717,25 +1717,25 @@
         <v>165</v>
       </c>
       <c r="E35" t="n">
-        <v>0.1694369337011029</v>
+        <v>0.1523016141160933</v>
       </c>
       <c r="F35" t="n">
-        <v>0.1433185982828986</v>
+        <v>0.1256444321700585</v>
       </c>
       <c r="G35" t="n">
-        <v>6.487279184836812</v>
+        <v>5.713342634056928</v>
       </c>
       <c r="H35" t="n">
         <v>0.001</v>
       </c>
       <c r="I35" t="n">
-        <v>757.6297216340317</v>
+        <v>639.1000296499849</v>
       </c>
       <c r="J35" t="n">
-        <v>4471.455573969113</v>
+        <v>4196.278768016373</v>
       </c>
       <c r="K35" t="n">
-        <v>3.784850847895308</v>
+        <v>3.237921027698854</v>
       </c>
     </row>
     <row r="36">
@@ -1754,25 +1754,25 @@
         <v>170</v>
       </c>
       <c r="E36" t="n">
-        <v>0.171514080247389</v>
+        <v>0.1805324117799927</v>
       </c>
       <c r="F36" t="n">
-        <v>0.1462553631817606</v>
+        <v>0.1555486438464558</v>
       </c>
       <c r="G36" t="n">
-        <v>6.790292626571371</v>
+        <v>7.22598818001572</v>
       </c>
       <c r="H36" t="n">
         <v>0.001</v>
       </c>
       <c r="I36" t="n">
-        <v>783.6740135721459</v>
+        <v>805.5186080965218</v>
       </c>
       <c r="J36" t="n">
-        <v>4569.152645903986</v>
+        <v>4461.905760602</v>
       </c>
       <c r="K36" t="n">
-        <v>3.80708559309889</v>
+        <v>4.126753107596748</v>
       </c>
     </row>
     <row r="37">
@@ -1791,25 +1791,25 @@
         <v>174</v>
       </c>
       <c r="E37" t="n">
-        <v>0.1693885902118237</v>
+        <v>0.1774486907954965</v>
       </c>
       <c r="F37" t="n">
-        <v>0.1446680125395566</v>
+        <v>0.152967997069172</v>
       </c>
       <c r="G37" t="n">
-        <v>6.852129123254785</v>
+        <v>7.248515617214017</v>
       </c>
       <c r="H37" t="n">
         <v>0.001</v>
       </c>
       <c r="I37" t="n">
-        <v>789.6597658347648</v>
+        <v>812.6671136644674</v>
       </c>
       <c r="J37" t="n">
-        <v>4661.82382678361</v>
+        <v>4579.730118161528</v>
       </c>
       <c r="K37" t="n">
-        <v>3.760511996712126</v>
+        <v>4.076469854159391</v>
       </c>
     </row>
     <row r="38">
@@ -1828,25 +1828,25 @@
         <v>179</v>
       </c>
       <c r="E38" t="n">
-        <v>0.177518171400859</v>
+        <v>0.1866865354610838</v>
       </c>
       <c r="F38" t="n">
-        <v>0.1537470202852769</v>
+        <v>0.1631803659657394</v>
       </c>
       <c r="G38" t="n">
-        <v>7.467798700101443</v>
+        <v>7.94202285906509</v>
       </c>
       <c r="H38" t="n">
         <v>0.001</v>
       </c>
       <c r="I38" t="n">
-        <v>849.364234086714</v>
+        <v>888.8960647038859</v>
       </c>
       <c r="J38" t="n">
-        <v>4784.660789281901</v>
+        <v>4761.436396623168</v>
       </c>
       <c r="K38" t="n">
-        <v>4.007356341706271</v>
+        <v>4.366638798108564</v>
       </c>
     </row>
     <row r="39">
@@ -1865,25 +1865,25 @@
         <v>184</v>
       </c>
       <c r="E39" t="n">
-        <v>0.1830762476806235</v>
+        <v>0.1814949099839207</v>
       </c>
       <c r="F39" t="n">
-        <v>0.160128951267158</v>
+        <v>0.1585031939722331</v>
       </c>
       <c r="G39" t="n">
-        <v>7.978118397128177</v>
+        <v>7.893926225065565</v>
       </c>
       <c r="H39" t="n">
         <v>0.001</v>
       </c>
       <c r="I39" t="n">
-        <v>903.0324416441856</v>
+        <v>880.9954548466064</v>
       </c>
       <c r="J39" t="n">
-        <v>4932.548340293305</v>
+        <v>4854.105577531937</v>
       </c>
       <c r="K39" t="n">
-        <v>4.24946151396682</v>
+        <v>4.205615155331319</v>
       </c>
     </row>
     <row r="40">
@@ -1902,25 +1902,25 @@
         <v>188</v>
       </c>
       <c r="E40" t="n">
-        <v>0.1781275569864013</v>
+        <v>0.1888261267831572</v>
       </c>
       <c r="F40" t="n">
-        <v>0.155548643716797</v>
+        <v>0.1665411302662111</v>
       </c>
       <c r="G40" t="n">
-        <v>7.88911117463726</v>
+        <v>8.473240129948765</v>
       </c>
       <c r="H40" t="n">
         <v>0.001</v>
       </c>
       <c r="I40" t="n">
-        <v>903.3243832460312</v>
+        <v>937.9072095158523</v>
       </c>
       <c r="J40" t="n">
-        <v>5071.221985686321</v>
+        <v>4967.041507941956</v>
       </c>
       <c r="K40" t="n">
-        <v>4.153582946122677</v>
+        <v>4.429145188090675</v>
       </c>
     </row>
     <row r="41">
@@ -1939,25 +1939,25 @@
         <v>193</v>
       </c>
       <c r="E41" t="n">
-        <v>0.1796612794507079</v>
+        <v>0.1928483851718919</v>
       </c>
       <c r="F41" t="n">
-        <v>0.1577270890616894</v>
+        <v>0.1712667911925306</v>
       </c>
       <c r="G41" t="n">
-        <v>8.190923679620131</v>
+        <v>8.935780431988279</v>
       </c>
       <c r="H41" t="n">
         <v>0.001</v>
       </c>
       <c r="I41" t="n">
-        <v>929.8807269639427</v>
+        <v>986.363792289834</v>
       </c>
       <c r="J41" t="n">
-        <v>5175.743653874322</v>
+        <v>5114.711183143467</v>
       </c>
       <c r="K41" t="n">
-        <v>4.149894283544994</v>
+        <v>4.542367873475873</v>
       </c>
     </row>
     <row r="42">
@@ -1976,25 +1976,25 @@
         <v>198</v>
       </c>
       <c r="E42" t="n">
-        <v>0.1795415356998524</v>
+        <v>0.188363479786846</v>
       </c>
       <c r="F42" t="n">
-        <v>0.1581754298587027</v>
+        <v>0.1672271120729618</v>
       </c>
       <c r="G42" t="n">
-        <v>8.403100547881191</v>
+        <v>8.911818829831976</v>
       </c>
       <c r="H42" t="n">
         <v>0.001</v>
       </c>
       <c r="I42" t="n">
-        <v>943.4414661298529</v>
+        <v>988.2981664583608</v>
       </c>
       <c r="J42" t="n">
-        <v>5254.725389600355</v>
+        <v>5246.76103656998</v>
       </c>
       <c r="K42" t="n">
-        <v>4.150818474203922</v>
+        <v>4.396786209411307</v>
       </c>
     </row>
     <row r="43">
@@ -2013,25 +2013,25 @@
         <v>202</v>
       </c>
       <c r="E43" t="n">
-        <v>0.1812747727109282</v>
+        <v>0.187844403013537</v>
       </c>
       <c r="F43" t="n">
-        <v>0.1603889250760029</v>
+        <v>0.1671261479883721</v>
       </c>
       <c r="G43" t="n">
-        <v>8.679311267587746</v>
+        <v>9.066613128633509</v>
       </c>
       <c r="H43" t="n">
         <v>0.001</v>
       </c>
       <c r="I43" t="n">
-        <v>981.286032853209</v>
+        <v>999.8139063199339</v>
       </c>
       <c r="J43" t="n">
-        <v>5413.25203820847</v>
+        <v>5322.564262124342</v>
       </c>
       <c r="K43" t="n">
-        <v>4.266463213271111</v>
+        <v>4.361917920560377</v>
       </c>
     </row>
     <row r="44">
@@ -2050,25 +2050,25 @@
         <v>207</v>
       </c>
       <c r="E44" t="n">
-        <v>0.1792090753792352</v>
+        <v>0.1888711837942516</v>
       </c>
       <c r="F44" t="n">
-        <v>0.1587913906871763</v>
+        <v>0.1686938500577903</v>
       </c>
       <c r="G44" t="n">
-        <v>8.777149715165111</v>
+        <v>9.360562017812709</v>
       </c>
       <c r="H44" t="n">
         <v>0.001</v>
       </c>
       <c r="I44" t="n">
-        <v>987.7082951914931</v>
+        <v>1028.572489820757</v>
       </c>
       <c r="J44" t="n">
-        <v>5511.485917224581</v>
+        <v>5445.894228847746</v>
       </c>
       <c r="K44" t="n">
-        <v>4.179563987248722</v>
+        <v>4.389608069601873</v>
       </c>
     </row>
     <row r="45">
@@ -2087,25 +2087,25 @@
         <v>212</v>
       </c>
       <c r="E45" t="n">
-        <v>0.1827729557245518</v>
+        <v>0.1943698516063707</v>
       </c>
       <c r="F45" t="n">
-        <v>0.1629373478537886</v>
+        <v>0.1748157217909915</v>
       </c>
       <c r="G45" t="n">
-        <v>9.214386416357321</v>
+        <v>9.940092115656233</v>
       </c>
       <c r="H45" t="n">
         <v>0.001</v>
       </c>
       <c r="I45" t="n">
-        <v>1038.665484704141</v>
+        <v>1098.768322025674</v>
       </c>
       <c r="J45" t="n">
-        <v>5682.818229790315</v>
+        <v>5652.977110106825</v>
       </c>
       <c r="K45" t="n">
-        <v>4.284264848007727</v>
+        <v>4.623652537044055</v>
       </c>
     </row>
     <row r="46">
@@ -2124,25 +2124,25 @@
         <v>216</v>
       </c>
       <c r="E46" t="n">
-        <v>0.1864715475029139</v>
+        <v>0.1965238362362337</v>
       </c>
       <c r="F46" t="n">
-        <v>0.1671018224434596</v>
+        <v>0.1773934513847154</v>
       </c>
       <c r="G46" t="n">
-        <v>9.62695892329646</v>
+        <v>10.27286370669313</v>
       </c>
       <c r="H46" t="n">
         <v>0.001</v>
       </c>
       <c r="I46" t="n">
-        <v>1078.661888003911</v>
+        <v>1126.205494710873</v>
       </c>
       <c r="J46" t="n">
-        <v>5784.59235442906</v>
+        <v>5730.630524416922</v>
       </c>
       <c r="K46" t="n">
-        <v>4.383673373597494</v>
+        <v>4.656005089795618</v>
       </c>
     </row>
     <row r="47">
@@ -2161,25 +2161,25 @@
         <v>221</v>
       </c>
       <c r="E47" t="n">
-        <v>0.1892552850394244</v>
+        <v>0.1949041271119488</v>
       </c>
       <c r="F47" t="n">
-        <v>0.1704007567845274</v>
+        <v>0.1761809672773428</v>
       </c>
       <c r="G47" t="n">
-        <v>10.03765686846443</v>
+        <v>10.40978813585243</v>
       </c>
       <c r="H47" t="n">
         <v>0.001</v>
       </c>
       <c r="I47" t="n">
-        <v>1113.660895912224</v>
+        <v>1143.521701290344</v>
       </c>
       <c r="J47" t="n">
-        <v>5884.437497638352</v>
+        <v>5867.098445963282</v>
       </c>
       <c r="K47" t="n">
-        <v>4.436159608725032</v>
+        <v>4.560324768272891</v>
       </c>
     </row>
     <row r="48">
@@ -2198,25 +2198,25 @@
         <v>226</v>
       </c>
       <c r="E48" t="n">
-        <v>0.1827320963727195</v>
+        <v>0.1938227571238266</v>
       </c>
       <c r="F48" t="n">
-        <v>0.1641578258357358</v>
+        <v>0.1755005470584591</v>
       </c>
       <c r="G48" t="n">
-        <v>9.8379150884487</v>
+        <v>10.57856865696503</v>
       </c>
       <c r="H48" t="n">
         <v>0.001</v>
       </c>
       <c r="I48" t="n">
-        <v>1086.777967975353</v>
+        <v>1153.967281963643</v>
       </c>
       <c r="J48" t="n">
-        <v>5947.384118872291</v>
+        <v>5953.724418574922</v>
       </c>
       <c r="K48" t="n">
-        <v>4.239419664537203</v>
+        <v>4.51404346325082</v>
       </c>
     </row>
     <row r="49">
@@ -2235,25 +2235,25 @@
         <v>230</v>
       </c>
       <c r="E49" t="n">
-        <v>0.1836871092610974</v>
+        <v>0.1864351717766692</v>
       </c>
       <c r="F49" t="n">
-        <v>0.1654658393785327</v>
+        <v>0.1682752425752556</v>
       </c>
       <c r="G49" t="n">
-        <v>10.08091699672701</v>
+        <v>10.26629397663932</v>
       </c>
       <c r="H49" t="n">
         <v>0.001</v>
       </c>
       <c r="I49" t="n">
-        <v>1112.638782561444</v>
+        <v>1129.748906081588</v>
       </c>
       <c r="J49" t="n">
-        <v>6057.250217705322</v>
+        <v>6059.741277975782</v>
       </c>
       <c r="K49" t="n">
-        <v>4.265071278523682</v>
+        <v>4.346852164633938</v>
       </c>
     </row>
     <row r="50">
@@ -2272,25 +2272,25 @@
         <v>11</v>
       </c>
       <c r="E50" t="n">
-        <v>0.4540647766946753</v>
+        <v>0.5042739129028468</v>
       </c>
       <c r="F50" t="n">
-        <v>-0.09187044661064947</v>
+        <v>0.008547825805693687</v>
       </c>
       <c r="G50" t="n">
-        <v>0.8317191441606815</v>
+        <v>1.017243042131891</v>
       </c>
       <c r="H50" t="n">
-        <v>0.663</v>
+        <v>0.471</v>
       </c>
       <c r="I50" t="n">
-        <v>155.8593159772076</v>
+        <v>101.4748901356991</v>
       </c>
       <c r="J50" t="n">
-        <v>343.25348271181</v>
+        <v>201.2297038162456</v>
       </c>
       <c r="K50" t="n">
-        <v>9.152322810631675</v>
+        <v>3.902968091160643</v>
       </c>
     </row>
     <row r="51">
@@ -2309,25 +2309,25 @@
         <v>16</v>
       </c>
       <c r="E51" t="n">
-        <v>0.337553379043599</v>
+        <v>0.2966481564618892</v>
       </c>
       <c r="F51" t="n">
-        <v>0.006330068565398417</v>
+        <v>-0.05502776530716602</v>
       </c>
       <c r="G51" t="n">
-        <v>1.019111180780905</v>
+        <v>0.8435270602822149</v>
       </c>
       <c r="H51" t="n">
-        <v>0.448</v>
+        <v>0.662</v>
       </c>
       <c r="I51" t="n">
-        <v>149.7692047607856</v>
+        <v>91.23315384950106</v>
       </c>
       <c r="J51" t="n">
-        <v>443.6904325624929</v>
+        <v>307.5466739373514</v>
       </c>
       <c r="K51" t="n">
-        <v>6.19078208535838</v>
+        <v>3.080494560550398</v>
       </c>
     </row>
     <row r="52">
@@ -2346,25 +2346,25 @@
         <v>20</v>
       </c>
       <c r="E52" t="n">
-        <v>0.2690628190827337</v>
+        <v>0.2654594980853385</v>
       </c>
       <c r="F52" t="n">
-        <v>0.008013825897995597</v>
+        <v>0.003123604544387981</v>
       </c>
       <c r="G52" t="n">
-        <v>1.030698551257481</v>
+        <v>1.011906889683399</v>
       </c>
       <c r="H52" t="n">
-        <v>0.45</v>
+        <v>0.479</v>
       </c>
       <c r="I52" t="n">
-        <v>148.9924651300705</v>
+        <v>102.6262459548834</v>
       </c>
       <c r="J52" t="n">
-        <v>553.7460197510866</v>
+        <v>386.5985082285195</v>
       </c>
       <c r="K52" t="n">
-        <v>4.669555028397697</v>
+        <v>2.10644476558896</v>
       </c>
     </row>
     <row r="53">
@@ -2383,25 +2383,25 @@
         <v>25</v>
       </c>
       <c r="E53" t="n">
-        <v>0.2490882289063756</v>
+        <v>0.2609479173050455</v>
       </c>
       <c r="F53" t="n">
-        <v>0.05147986809226401</v>
+        <v>0.06646052712216277</v>
       </c>
       <c r="G53" t="n">
-        <v>1.260514625394269</v>
+        <v>1.341721522715009</v>
       </c>
       <c r="H53" t="n">
-        <v>0.173</v>
+        <v>0.152</v>
       </c>
       <c r="I53" t="n">
-        <v>177.0048403230225</v>
+        <v>121.4872235431336</v>
       </c>
       <c r="J53" t="n">
-        <v>710.6110196381584</v>
+        <v>465.5611924318072</v>
       </c>
       <c r="K53" t="n">
-        <v>3.981816140151957</v>
+        <v>2.423228082882431</v>
       </c>
     </row>
     <row r="54">
@@ -2420,25 +2420,25 @@
         <v>30</v>
       </c>
       <c r="E54" t="n">
-        <v>0.2290282931613529</v>
+        <v>0.1818257080951598</v>
       </c>
       <c r="F54" t="n">
-        <v>0.06840918756996806</v>
+        <v>0.01137273061498478</v>
       </c>
       <c r="G54" t="n">
-        <v>1.425909404227422</v>
+        <v>1.066720633356537</v>
       </c>
       <c r="H54" t="n">
-        <v>0.082</v>
+        <v>0.398</v>
       </c>
       <c r="I54" t="n">
-        <v>187.9845131799059</v>
+        <v>101.0275905128577</v>
       </c>
       <c r="J54" t="n">
-        <v>820.7916610873438</v>
+        <v>555.628747833525</v>
       </c>
       <c r="K54" t="n">
-        <v>3.660958835599077</v>
+        <v>1.390357751478525</v>
       </c>
     </row>
     <row r="55">
@@ -2457,25 +2457,25 @@
         <v>34</v>
       </c>
       <c r="E55" t="n">
-        <v>0.2256937344639147</v>
+        <v>0.1676593553039323</v>
       </c>
       <c r="F55" t="n">
-        <v>0.08742475847532805</v>
+        <v>0.01902709732249164</v>
       </c>
       <c r="G55" t="n">
-        <v>1.63228036405321</v>
+        <v>1.128014588359867</v>
       </c>
       <c r="H55" t="n">
-        <v>0.027</v>
+        <v>0.277</v>
       </c>
       <c r="I55" t="n">
-        <v>199.8354509940641</v>
+        <v>108.1603690918435</v>
       </c>
       <c r="J55" t="n">
-        <v>885.4275528238688</v>
+        <v>645.1197960040508</v>
       </c>
       <c r="K55" t="n">
-        <v>3.447740269724831</v>
+        <v>1.322822848148824</v>
       </c>
     </row>
     <row r="56">
@@ -2494,25 +2494,25 @@
         <v>39</v>
       </c>
       <c r="E56" t="n">
-        <v>0.2041629597528989</v>
+        <v>0.1469969673256371</v>
       </c>
       <c r="F56" t="n">
-        <v>0.08358159001848953</v>
+        <v>0.01775408358709718</v>
       </c>
       <c r="G56" t="n">
-        <v>1.693155088572847</v>
+        <v>1.137369912164867</v>
       </c>
       <c r="H56" t="n">
-        <v>0.026</v>
+        <v>0.281</v>
       </c>
       <c r="I56" t="n">
-        <v>194.4687604532768</v>
+        <v>115.7263833573242</v>
       </c>
       <c r="J56" t="n">
-        <v>952.5173454021478</v>
+        <v>787.2705502893788</v>
       </c>
       <c r="K56" t="n">
-        <v>3.037457404256481</v>
+        <v>1.275245289219449</v>
       </c>
     </row>
     <row r="57">
@@ -2531,25 +2531,25 @@
         <v>44</v>
       </c>
       <c r="E57" t="n">
-        <v>0.2171090769975938</v>
+        <v>0.1687476343566744</v>
       </c>
       <c r="F57" t="n">
-        <v>0.1140971134446457</v>
+        <v>0.05937232308781581</v>
       </c>
       <c r="G57" t="n">
-        <v>2.107610315436806</v>
+        <v>1.54283112339558</v>
       </c>
       <c r="H57" t="n">
-        <v>0.005</v>
+        <v>0.044</v>
       </c>
       <c r="I57" t="n">
-        <v>237.7647795625752</v>
+        <v>152.4526113317228</v>
       </c>
       <c r="J57" t="n">
-        <v>1095.139746576373</v>
+        <v>903.4355468918189</v>
       </c>
       <c r="K57" t="n">
-        <v>3.535853256994268</v>
+        <v>1.782592630980634</v>
       </c>
     </row>
     <row r="58">
@@ -2568,25 +2568,25 @@
         <v>48</v>
       </c>
       <c r="E58" t="n">
-        <v>0.2164837485069393</v>
+        <v>0.149108946425533</v>
       </c>
       <c r="F58" t="n">
-        <v>0.123208004281575</v>
+        <v>0.0478123924285726</v>
       </c>
       <c r="G58" t="n">
-        <v>2.320900790498021</v>
+        <v>1.472004135797229</v>
       </c>
       <c r="H58" t="n">
-        <v>0.002</v>
+        <v>0.034</v>
       </c>
       <c r="I58" t="n">
-        <v>265.813545913641</v>
+        <v>150.7256656452056</v>
       </c>
       <c r="J58" t="n">
-        <v>1227.868363084633</v>
+        <v>1010.842536671534</v>
       </c>
       <c r="K58" t="n">
-        <v>3.467782559166384</v>
+        <v>1.562596092827975</v>
       </c>
     </row>
     <row r="59">
@@ -2605,25 +2605,25 @@
         <v>53</v>
       </c>
       <c r="E59" t="n">
-        <v>0.2491154112060493</v>
+        <v>0.1482641801720487</v>
       </c>
       <c r="F59" t="n">
-        <v>0.1692340719726503</v>
+        <v>0.05765398657333054</v>
       </c>
       <c r="G59" t="n">
-        <v>3.118568286370094</v>
+        <v>1.636285877819227</v>
       </c>
       <c r="H59" t="n">
-        <v>0.001</v>
+        <v>0.017</v>
       </c>
       <c r="I59" t="n">
-        <v>355.863744313806</v>
+        <v>159.3291901584869</v>
       </c>
       <c r="J59" t="n">
-        <v>1428.509551420176</v>
+        <v>1074.630365699916</v>
       </c>
       <c r="K59" t="n">
-        <v>4.898928794356264</v>
+        <v>1.596867729615576</v>
       </c>
     </row>
     <row r="60">
@@ -2642,25 +2642,25 @@
         <v>58</v>
       </c>
       <c r="E60" t="n">
-        <v>0.2611641873873121</v>
+        <v>0.1345602321711464</v>
       </c>
       <c r="F60" t="n">
-        <v>0.1901222823283997</v>
+        <v>0.05134486987991038</v>
       </c>
       <c r="G60" t="n">
-        <v>3.676199099260341</v>
+        <v>1.617011913019311</v>
       </c>
       <c r="H60" t="n">
-        <v>0.001</v>
+        <v>0.016</v>
       </c>
       <c r="I60" t="n">
-        <v>414.5751402959819</v>
+        <v>152.8027835636105</v>
       </c>
       <c r="J60" t="n">
-        <v>1587.411905297559</v>
+        <v>1135.571640284192</v>
       </c>
       <c r="K60" t="n">
-        <v>5.421913695254558</v>
+        <v>1.424204211940749</v>
       </c>
     </row>
     <row r="61">
@@ -2679,25 +2679,25 @@
         <v>62</v>
       </c>
       <c r="E61" t="n">
-        <v>0.2596740034226862</v>
+        <v>0.1401088636947223</v>
       </c>
       <c r="F61" t="n">
-        <v>0.1935734680139976</v>
+        <v>0.0633328693817512</v>
       </c>
       <c r="G61" t="n">
-        <v>3.928470500536262</v>
+        <v>1.824904580507023</v>
       </c>
       <c r="H61" t="n">
-        <v>0.001</v>
+        <v>0.008</v>
       </c>
       <c r="I61" t="n">
-        <v>450.9244023184474</v>
+        <v>179.5144878225149</v>
       </c>
       <c r="J61" t="n">
-        <v>1736.501907680192</v>
+        <v>1281.250044348742</v>
       </c>
       <c r="K61" t="n">
-        <v>5.542146240870014</v>
+        <v>1.495862608029784</v>
       </c>
     </row>
     <row r="62">
@@ -2716,25 +2716,25 @@
         <v>67</v>
       </c>
       <c r="E62" t="n">
-        <v>0.2286852390593461</v>
+        <v>0.1506097352590443</v>
       </c>
       <c r="F62" t="n">
-        <v>0.1654627176707678</v>
+        <v>0.0809875824114249</v>
       </c>
       <c r="G62" t="n">
-        <v>3.617148352148141</v>
+        <v>2.163244443024923</v>
       </c>
       <c r="H62" t="n">
-        <v>0.001</v>
+        <v>0.003</v>
       </c>
       <c r="I62" t="n">
-        <v>423.7689487047983</v>
+        <v>223.1196706475193</v>
       </c>
       <c r="J62" t="n">
-        <v>1853.066470087412</v>
+        <v>1481.442552593031</v>
       </c>
       <c r="K62" t="n">
-        <v>4.831600427020523</v>
+        <v>2.24090961559351</v>
       </c>
     </row>
     <row r="63">
@@ -2753,25 +2753,25 @@
         <v>72</v>
       </c>
       <c r="E63" t="n">
-        <v>0.2007699431303815</v>
+        <v>0.1677506624327929</v>
       </c>
       <c r="F63" t="n">
-        <v>0.1402222115493499</v>
+        <v>0.104701470192853</v>
       </c>
       <c r="G63" t="n">
-        <v>3.315895375232826</v>
+        <v>2.660631428780263</v>
       </c>
       <c r="H63" t="n">
         <v>0.001</v>
       </c>
       <c r="I63" t="n">
-        <v>400.7771584283195</v>
+        <v>276.3840127261318</v>
       </c>
       <c r="J63" t="n">
-        <v>1996.200985961587</v>
+        <v>1647.58820452862</v>
       </c>
       <c r="K63" t="n">
-        <v>4.300665574403083</v>
+        <v>2.767721545806567</v>
       </c>
     </row>
     <row r="64">
@@ -2790,25 +2790,25 @@
         <v>76</v>
       </c>
       <c r="E64" t="n">
-        <v>0.2008168961751941</v>
+        <v>0.1645950767537591</v>
       </c>
       <c r="F64" t="n">
-        <v>0.1437323887591366</v>
+        <v>0.1049232965218847</v>
       </c>
       <c r="G64" t="n">
-        <v>3.51788786949759</v>
+        <v>2.758340309509298</v>
       </c>
       <c r="H64" t="n">
         <v>0.001</v>
       </c>
       <c r="I64" t="n">
-        <v>429.6952753753981</v>
+        <v>284.0333743226835</v>
       </c>
       <c r="J64" t="n">
-        <v>2139.736663395737</v>
+        <v>1725.649271682706</v>
       </c>
       <c r="K64" t="n">
-        <v>4.405752670014369</v>
+        <v>2.687765153834455</v>
       </c>
     </row>
     <row r="65">
@@ -2827,25 +2827,25 @@
         <v>81</v>
       </c>
       <c r="E65" t="n">
-        <v>0.179415035002062</v>
+        <v>0.1794556844377696</v>
       </c>
       <c r="F65" t="n">
-        <v>0.1247093706688661</v>
+        <v>0.1247527300669543</v>
       </c>
       <c r="G65" t="n">
-        <v>3.279642742464448</v>
+        <v>3.280548308621358</v>
       </c>
       <c r="H65" t="n">
         <v>0.001</v>
       </c>
       <c r="I65" t="n">
-        <v>407.3769694764215</v>
+        <v>340.421121789901</v>
       </c>
       <c r="J65" t="n">
-        <v>2270.584343568194</v>
+        <v>1896.964829263738</v>
       </c>
       <c r="K65" t="n">
-        <v>3.907193209204044</v>
+        <v>3.237074549161874</v>
       </c>
     </row>
     <row r="66">
@@ -2864,25 +2864,25 @@
         <v>86</v>
       </c>
       <c r="E66" t="n">
-        <v>0.1779500355663928</v>
+        <v>0.1649553184404655</v>
       </c>
       <c r="F66" t="n">
-        <v>0.1265719127892924</v>
+        <v>0.1127650258429946</v>
       </c>
       <c r="G66" t="n">
-        <v>3.463537123347494</v>
+        <v>3.160651343971564</v>
       </c>
       <c r="H66" t="n">
         <v>0.001</v>
       </c>
       <c r="I66" t="n">
-        <v>423.0218300961284</v>
+        <v>333.579261550729</v>
       </c>
       <c r="J66" t="n">
-        <v>2377.19441162067</v>
+        <v>2022.240111470683</v>
       </c>
       <c r="K66" t="n">
-        <v>3.875880155216719</v>
+        <v>2.9347424021878</v>
       </c>
     </row>
     <row r="67">
@@ -2901,25 +2901,25 @@
         <v>90</v>
       </c>
       <c r="E67" t="n">
-        <v>0.1801093091118439</v>
+        <v>0.1560905414672123</v>
       </c>
       <c r="F67" t="n">
-        <v>0.1313062917970728</v>
+        <v>0.1058578356021653</v>
       </c>
       <c r="G67" t="n">
-        <v>3.690536344303659</v>
+        <v>3.107348863239793</v>
       </c>
       <c r="H67" t="n">
         <v>0.001</v>
       </c>
       <c r="I67" t="n">
-        <v>444.3413602864088</v>
+        <v>329.4498598879989</v>
       </c>
       <c r="J67" t="n">
-        <v>2467.064931166232</v>
+        <v>2110.633077387342</v>
       </c>
       <c r="K67" t="n">
-        <v>3.990592698089626</v>
+        <v>2.763214469745415</v>
       </c>
     </row>
     <row r="68">
@@ -2938,25 +2938,25 @@
         <v>95</v>
       </c>
       <c r="E68" t="n">
-        <v>0.1812893623035288</v>
+        <v>0.1566144224839928</v>
       </c>
       <c r="F68" t="n">
-        <v>0.1352943826576597</v>
+        <v>0.1092332102639925</v>
       </c>
       <c r="G68" t="n">
-        <v>3.941503261863284</v>
+        <v>3.305411895263482</v>
       </c>
       <c r="H68" t="n">
         <v>0.001</v>
       </c>
       <c r="I68" t="n">
-        <v>471.4850423811632</v>
+        <v>355.0120681327314</v>
       </c>
       <c r="J68" t="n">
-        <v>2600.731981128414</v>
+        <v>2266.790391983321</v>
       </c>
       <c r="K68" t="n">
-        <v>4.092750561468098</v>
+        <v>2.833357405306586</v>
       </c>
     </row>
     <row r="69">
@@ -2975,25 +2975,25 @@
         <v>100</v>
       </c>
       <c r="E69" t="n">
-        <v>0.1748967880624035</v>
+        <v>0.1546395804306359</v>
       </c>
       <c r="F69" t="n">
-        <v>0.1310083193423186</v>
+        <v>0.1096736006663082</v>
       </c>
       <c r="G69" t="n">
-        <v>3.985028258285178</v>
+        <v>3.439035049188756</v>
       </c>
       <c r="H69" t="n">
         <v>0.001</v>
       </c>
       <c r="I69" t="n">
-        <v>482.4602509001276</v>
+        <v>359.9370935525363</v>
       </c>
       <c r="J69" t="n">
-        <v>2758.542659616967</v>
+        <v>2327.587106419932</v>
       </c>
       <c r="K69" t="n">
-        <v>3.915466250254436</v>
+        <v>2.746880925123897</v>
       </c>
     </row>
     <row r="70">
@@ -3012,25 +3012,25 @@
         <v>104</v>
       </c>
       <c r="E70" t="n">
-        <v>0.1693897411386435</v>
+        <v>0.1497828348854159</v>
       </c>
       <c r="F70" t="n">
-        <v>0.1270116667069416</v>
+        <v>0.1064044080938555</v>
       </c>
       <c r="G70" t="n">
-        <v>3.99710801895066</v>
+        <v>3.452933772936118</v>
       </c>
       <c r="H70" t="n">
         <v>0.001</v>
       </c>
       <c r="I70" t="n">
-        <v>480.3095104593779</v>
+        <v>364.4547814147135</v>
       </c>
       <c r="J70" t="n">
-        <v>2835.528924188215</v>
+        <v>2433.221281287152</v>
       </c>
       <c r="K70" t="n">
-        <v>3.734636310543169</v>
+        <v>2.748546050348216</v>
       </c>
     </row>
     <row r="71">
@@ -3049,25 +3049,25 @@
         <v>109</v>
       </c>
       <c r="E71" t="n">
-        <v>0.1719684363777775</v>
+        <v>0.1448825951666754</v>
       </c>
       <c r="F71" t="n">
-        <v>0.131772729405825</v>
+        <v>0.1033720415339898</v>
       </c>
       <c r="G71" t="n">
-        <v>4.278278685277815</v>
+        <v>3.490259283186095</v>
       </c>
       <c r="H71" t="n">
         <v>0.001</v>
       </c>
       <c r="I71" t="n">
-        <v>512.6168055202979</v>
+        <v>368.9325122374968</v>
       </c>
       <c r="J71" t="n">
-        <v>2980.877283748686</v>
+        <v>2546.42396357596</v>
       </c>
       <c r="K71" t="n">
-        <v>3.864156970198027</v>
+        <v>2.604856506828096</v>
       </c>
     </row>
     <row r="72">
@@ -3086,25 +3086,25 @@
         <v>114</v>
       </c>
       <c r="E72" t="n">
-        <v>0.1656348374493649</v>
+        <v>0.1419337867009056</v>
       </c>
       <c r="F72" t="n">
-        <v>0.1270068206646133</v>
+        <v>0.1022084990481698</v>
       </c>
       <c r="G72" t="n">
-        <v>4.287945673533751</v>
+        <v>3.572882541257841</v>
       </c>
       <c r="H72" t="n">
         <v>0.001</v>
       </c>
       <c r="I72" t="n">
-        <v>514.5086984406421</v>
+        <v>379.2516364397864</v>
       </c>
       <c r="J72" t="n">
-        <v>3106.283112681106</v>
+        <v>2672.032116207653</v>
       </c>
       <c r="K72" t="n">
-        <v>3.729092756402999</v>
+        <v>2.550314473249522</v>
       </c>
     </row>
     <row r="73">
@@ -3123,25 +3123,25 @@
         <v>118</v>
       </c>
       <c r="E73" t="n">
-        <v>0.1659716421051018</v>
+        <v>0.151262013971253</v>
       </c>
       <c r="F73" t="n">
-        <v>0.1287382332705082</v>
+        <v>0.1133719253092553</v>
       </c>
       <c r="G73" t="n">
-        <v>4.457599970027377</v>
+        <v>3.992126155222307</v>
       </c>
       <c r="H73" t="n">
         <v>0.001</v>
       </c>
       <c r="I73" t="n">
-        <v>535.5348976590851</v>
+        <v>429.2740675048523</v>
       </c>
       <c r="J73" t="n">
-        <v>3226.665054744453</v>
+        <v>2837.950231089974</v>
       </c>
       <c r="K73" t="n">
-        <v>3.68175347146555</v>
+        <v>2.900720690521111</v>
       </c>
     </row>
     <row r="74">
@@ -3160,25 +3160,25 @@
         <v>123</v>
       </c>
       <c r="E74" t="n">
-        <v>0.1708156489504472</v>
+        <v>0.1465969415152222</v>
       </c>
       <c r="F74" t="n">
-        <v>0.1353804202731158</v>
+        <v>0.1101267253406589</v>
       </c>
       <c r="G74" t="n">
-        <v>4.820503643587934</v>
+        <v>4.019634564641517</v>
       </c>
       <c r="H74" t="n">
         <v>0.001</v>
       </c>
       <c r="I74" t="n">
-        <v>574.8974300223044</v>
+        <v>441.8323448208064</v>
       </c>
       <c r="J74" t="n">
-        <v>3365.601650403116</v>
+        <v>3013.926076861077</v>
       </c>
       <c r="K74" t="n">
-        <v>3.825871802688662</v>
+        <v>2.896854663869406</v>
       </c>
     </row>
     <row r="75">
@@ -3197,25 +3197,25 @@
         <v>128</v>
       </c>
       <c r="E75" t="n">
-        <v>0.1679189404399183</v>
+        <v>0.1407894527660243</v>
       </c>
       <c r="F75" t="n">
-        <v>0.1338172576710626</v>
+        <v>0.1055759057482385</v>
       </c>
       <c r="G75" t="n">
-        <v>4.924066110698629</v>
+        <v>3.998161636341644</v>
       </c>
       <c r="H75" t="n">
         <v>0.001</v>
       </c>
       <c r="I75" t="n">
-        <v>582.717380709445</v>
+        <v>440.9339315218399</v>
       </c>
       <c r="J75" t="n">
-        <v>3470.23021454773</v>
+        <v>3131.867642490386</v>
       </c>
       <c r="K75" t="n">
-        <v>3.70162644333443</v>
+        <v>2.698532081920324</v>
       </c>
     </row>
     <row r="76">
@@ -3234,25 +3234,25 @@
         <v>132</v>
       </c>
       <c r="E76" t="n">
-        <v>0.1898143693767539</v>
+        <v>0.1528967118169647</v>
       </c>
       <c r="F76" t="n">
-        <v>0.1576641459393234</v>
+        <v>0.1192815019684315</v>
       </c>
       <c r="G76" t="n">
-        <v>5.903982899097537</v>
+        <v>4.548438415404879</v>
       </c>
       <c r="H76" t="n">
         <v>0.001</v>
       </c>
       <c r="I76" t="n">
-        <v>694.3279792393391</v>
+        <v>502.1719623564679</v>
       </c>
       <c r="J76" t="n">
-        <v>3657.931596639026</v>
+        <v>3284.386932778691</v>
       </c>
       <c r="K76" t="n">
-        <v>4.402790676006603</v>
+        <v>3.114672593397253</v>
       </c>
     </row>
     <row r="77">
@@ -3271,25 +3271,25 @@
         <v>137</v>
       </c>
       <c r="E77" t="n">
-        <v>0.186673893090113</v>
+        <v>0.1490845495695475</v>
       </c>
       <c r="F77" t="n">
-        <v>0.1556309119103463</v>
+        <v>0.1166068606218204</v>
       </c>
       <c r="G77" t="n">
-        <v>6.013400968454151</v>
+        <v>4.590368169653294</v>
       </c>
       <c r="H77" t="n">
         <v>0.001</v>
       </c>
       <c r="I77" t="n">
-        <v>703.1646919310977</v>
+        <v>520.5474031994795</v>
       </c>
       <c r="J77" t="n">
-        <v>3766.807882405171</v>
+        <v>3491.625421295891</v>
       </c>
       <c r="K77" t="n">
-        <v>4.252153723259525</v>
+        <v>3.129747838091092</v>
       </c>
     </row>
     <row r="78">
@@ -3308,25 +3308,25 @@
         <v>142</v>
       </c>
       <c r="E78" t="n">
-        <v>0.1865757374183128</v>
+        <v>0.1534325856987356</v>
       </c>
       <c r="F78" t="n">
-        <v>0.1566704336469271</v>
+        <v>0.1223087837023655</v>
       </c>
       <c r="G78" t="n">
-        <v>6.238884541839532</v>
+        <v>4.929750732787415</v>
       </c>
       <c r="H78" t="n">
         <v>0.001</v>
       </c>
       <c r="I78" t="n">
-        <v>724.8835435249121</v>
+        <v>562.3563246871383</v>
       </c>
       <c r="J78" t="n">
-        <v>3885.197258525015</v>
+        <v>3665.168791402129</v>
       </c>
       <c r="K78" t="n">
-        <v>4.240454106634712</v>
+        <v>3.321285742448989</v>
       </c>
     </row>
     <row r="79">
@@ -3345,25 +3345,25 @@
         <v>146</v>
       </c>
       <c r="E79" t="n">
-        <v>0.1843405653621116</v>
+        <v>0.168289345053309</v>
       </c>
       <c r="F79" t="n">
-        <v>0.1552098712679011</v>
+        <v>0.1385853930909271</v>
       </c>
       <c r="G79" t="n">
-        <v>6.328052629502882</v>
+        <v>5.665554040298638</v>
       </c>
       <c r="H79" t="n">
         <v>0.001</v>
       </c>
       <c r="I79" t="n">
-        <v>735.440306116639</v>
+        <v>644.7108122577132</v>
       </c>
       <c r="J79" t="n">
-        <v>3989.573888264735</v>
+        <v>3830.966316099741</v>
       </c>
       <c r="K79" t="n">
-        <v>4.120503580109239</v>
+        <v>3.823402579158988</v>
       </c>
     </row>
     <row r="80">
@@ -3382,25 +3382,25 @@
         <v>151</v>
       </c>
       <c r="E80" t="n">
-        <v>0.1964941516440948</v>
+        <v>0.1720850554985721</v>
       </c>
       <c r="F80" t="n">
-        <v>0.1687870534249256</v>
+        <v>0.1435362643088677</v>
       </c>
       <c r="G80" t="n">
-        <v>7.091834377233714</v>
+        <v>6.027752781372806</v>
       </c>
       <c r="H80" t="n">
         <v>0.001</v>
       </c>
       <c r="I80" t="n">
-        <v>826.9751029509085</v>
+        <v>676.6237886045799</v>
       </c>
       <c r="J80" t="n">
-        <v>4208.649957423613</v>
+        <v>3931.914869912653</v>
       </c>
       <c r="K80" t="n">
-        <v>4.613896777623492</v>
+        <v>3.91224355456934</v>
       </c>
     </row>
     <row r="81">
@@ -3419,25 +3419,25 @@
         <v>156</v>
       </c>
       <c r="E81" t="n">
-        <v>0.1909420999615216</v>
+        <v>0.1747846511964646</v>
       </c>
       <c r="F81" t="n">
-        <v>0.1639735032935722</v>
+        <v>0.1472774729030133</v>
       </c>
       <c r="G81" t="n">
-        <v>7.080164471014019</v>
+        <v>6.354146882382218</v>
       </c>
       <c r="H81" t="n">
         <v>0.001</v>
       </c>
       <c r="I81" t="n">
-        <v>829.6509627524451</v>
+        <v>712.21156367652</v>
       </c>
       <c r="J81" t="n">
-        <v>4345.039480133692</v>
+        <v>4074.794661894924</v>
       </c>
       <c r="K81" t="n">
-        <v>4.416299335543783</v>
+        <v>3.979174807429905</v>
       </c>
     </row>
     <row r="82">
@@ -3456,25 +3456,25 @@
         <v>160</v>
       </c>
       <c r="E82" t="n">
-        <v>0.1876318024444356</v>
+        <v>0.1821908268148074</v>
       </c>
       <c r="F82" t="n">
-        <v>0.1612562116147094</v>
+        <v>0.1556385809321712</v>
       </c>
       <c r="G82" t="n">
-        <v>7.113842630321995</v>
+        <v>6.861597607227316</v>
       </c>
       <c r="H82" t="n">
         <v>0.001</v>
       </c>
       <c r="I82" t="n">
-        <v>830.779001165884</v>
+        <v>769.2567972180793</v>
       </c>
       <c r="J82" t="n">
-        <v>4427.708897652928</v>
+        <v>4222.258665086418</v>
       </c>
       <c r="K82" t="n">
-        <v>4.367324964565431</v>
+        <v>4.222662205621352</v>
       </c>
     </row>
     <row r="83">
@@ -3493,25 +3493,25 @@
         <v>165</v>
       </c>
       <c r="E83" t="n">
-        <v>0.191259411292134</v>
+        <v>0.1888343459229176</v>
       </c>
       <c r="F83" t="n">
-        <v>0.1658273173076099</v>
+        <v>0.1633259920211225</v>
       </c>
       <c r="G83" t="n">
-        <v>7.520395741244072</v>
+        <v>7.402843266559401</v>
       </c>
       <c r="H83" t="n">
         <v>0.001</v>
       </c>
       <c r="I83" t="n">
-        <v>871.9509590643808</v>
+        <v>825.8447266220609</v>
       </c>
       <c r="J83" t="n">
-        <v>4558.996355648836</v>
+        <v>4373.381985071569</v>
       </c>
       <c r="K83" t="n">
-        <v>4.470009394257567</v>
+        <v>4.39233685854913</v>
       </c>
     </row>
     <row r="84">
@@ -3530,25 +3530,25 @@
         <v>170</v>
       </c>
       <c r="E84" t="n">
-        <v>0.1977795627045713</v>
+        <v>0.2012078875131355</v>
       </c>
       <c r="F84" t="n">
-        <v>0.1733216225431253</v>
+        <v>0.1768544694495117</v>
       </c>
       <c r="G84" t="n">
-        <v>8.086517564399758</v>
+        <v>8.261997843073807</v>
       </c>
       <c r="H84" t="n">
         <v>0.001</v>
       </c>
       <c r="I84" t="n">
-        <v>928.9421551934228</v>
+        <v>914.3137022691628</v>
       </c>
       <c r="J84" t="n">
-        <v>4696.856148787268</v>
+        <v>4544.124554806399</v>
       </c>
       <c r="K84" t="n">
-        <v>4.65087267708746</v>
+        <v>4.729378160306549</v>
       </c>
     </row>
     <row r="85">
@@ -3567,25 +3567,25 @@
         <v>174</v>
       </c>
       <c r="E85" t="n">
-        <v>0.2011093034817222</v>
+        <v>0.2055010768299387</v>
       </c>
       <c r="F85" t="n">
-        <v>0.1773327946567735</v>
+        <v>0.1818552755451155</v>
       </c>
       <c r="G85" t="n">
-        <v>8.45831930004365</v>
+        <v>8.690806217754899</v>
       </c>
       <c r="H85" t="n">
         <v>0.001</v>
       </c>
       <c r="I85" t="n">
-        <v>963.7787172298434</v>
+        <v>961.142951123591</v>
       </c>
       <c r="J85" t="n">
-        <v>4792.312939005513</v>
+        <v>4677.070144595786</v>
       </c>
       <c r="K85" t="n">
-        <v>4.745112312625917</v>
+        <v>4.908722815592427</v>
       </c>
     </row>
     <row r="86">
@@ -3604,25 +3604,25 @@
         <v>179</v>
       </c>
       <c r="E86" t="n">
-        <v>0.1967908023501508</v>
+        <v>0.1987714370095047</v>
       </c>
       <c r="F86" t="n">
-        <v>0.1735766636897504</v>
+        <v>0.1756145421253863</v>
       </c>
       <c r="G86" t="n">
-        <v>8.477195954974007</v>
+        <v>8.583682657117713</v>
       </c>
       <c r="H86" t="n">
         <v>0.001</v>
       </c>
       <c r="I86" t="n">
-        <v>967.3026022796018</v>
+        <v>943.4880887690178</v>
       </c>
       <c r="J86" t="n">
-        <v>4915.385224958205</v>
+        <v>4746.597916499959</v>
       </c>
       <c r="K86" t="n">
-        <v>4.622249544946817</v>
+        <v>4.663668706038773</v>
       </c>
     </row>
     <row r="87">
@@ -3641,25 +3641,25 @@
         <v>184</v>
       </c>
       <c r="E87" t="n">
-        <v>0.1998056512523497</v>
+        <v>0.1967275407975825</v>
       </c>
       <c r="F87" t="n">
-        <v>0.1773282819055056</v>
+        <v>0.1741637076739191</v>
       </c>
       <c r="G87" t="n">
-        <v>8.889191976569229</v>
+        <v>8.718711032801785</v>
       </c>
       <c r="H87" t="n">
         <v>0.001</v>
       </c>
       <c r="I87" t="n">
-        <v>1003.080298397619</v>
+        <v>967.1574683655841</v>
       </c>
       <c r="J87" t="n">
-        <v>5020.279917562256</v>
+        <v>4916.228121616763</v>
       </c>
       <c r="K87" t="n">
-        <v>4.709001941985292</v>
+        <v>4.65635620396491</v>
       </c>
     </row>
     <row r="88">
@@ -3678,25 +3678,25 @@
         <v>188</v>
       </c>
       <c r="E88" t="n">
-        <v>0.2003347081567015</v>
+        <v>0.1955789478378163</v>
       </c>
       <c r="F88" t="n">
-        <v>0.1783658814577099</v>
+        <v>0.1734794683828113</v>
       </c>
       <c r="G88" t="n">
-        <v>9.119044494346888</v>
+        <v>8.849934598505756</v>
       </c>
       <c r="H88" t="n">
         <v>0.001</v>
       </c>
       <c r="I88" t="n">
-        <v>1016.214231057631</v>
+        <v>976.0468205389818</v>
       </c>
       <c r="J88" t="n">
-        <v>5072.581982462818</v>
+        <v>4990.551546214308</v>
       </c>
       <c r="K88" t="n">
-        <v>4.67436152302521</v>
+        <v>4.587497888307963</v>
       </c>
     </row>
     <row r="89">
@@ -3715,25 +3715,25 @@
         <v>193</v>
       </c>
       <c r="E89" t="n">
-        <v>0.2004832439013847</v>
+        <v>0.1967642950820772</v>
       </c>
       <c r="F89" t="n">
-        <v>0.1791057905297638</v>
+        <v>0.1752874045762502</v>
       </c>
       <c r="G89" t="n">
-        <v>9.378256634044764</v>
+        <v>9.161675198217997</v>
       </c>
       <c r="H89" t="n">
         <v>0.001</v>
       </c>
       <c r="I89" t="n">
-        <v>1035.149830666142</v>
+        <v>1001.300554850719</v>
       </c>
       <c r="J89" t="n">
-        <v>5163.273551057066</v>
+        <v>5088.832577236851</v>
       </c>
       <c r="K89" t="n">
-        <v>4.631984768158489</v>
+        <v>4.585869505958987</v>
       </c>
     </row>
     <row r="90">
@@ -3752,25 +3752,25 @@
         <v>198</v>
       </c>
       <c r="E90" t="n">
-        <v>0.196677050047656</v>
+        <v>0.1939583217957061</v>
       </c>
       <c r="F90" t="n">
-        <v>0.1757571815593136</v>
+        <v>0.1729676530924693</v>
       </c>
       <c r="G90" t="n">
-        <v>9.401447726942227</v>
+        <v>9.240216428445523</v>
       </c>
       <c r="H90" t="n">
         <v>0.001</v>
       </c>
       <c r="I90" t="n">
-        <v>1044.160908794897</v>
+        <v>1010.244210606835</v>
       </c>
       <c r="J90" t="n">
-        <v>5309.012457436651</v>
+        <v>5208.563372036764</v>
       </c>
       <c r="K90" t="n">
-        <v>4.565004657665564</v>
+        <v>4.512554784940402</v>
       </c>
     </row>
     <row r="91">
@@ -3789,25 +3789,25 @@
         <v>202</v>
       </c>
       <c r="E91" t="n">
-        <v>0.1910186752401954</v>
+        <v>0.1928465981161138</v>
       </c>
       <c r="F91" t="n">
-        <v>0.1703813965473432</v>
+        <v>0.1722559501088718</v>
       </c>
       <c r="G91" t="n">
-        <v>9.256001146428074</v>
+        <v>9.365737204981947</v>
       </c>
       <c r="H91" t="n">
         <v>0.001</v>
       </c>
       <c r="I91" t="n">
-        <v>1033.546991268668</v>
+        <v>1020.81860204309</v>
       </c>
       <c r="J91" t="n">
-        <v>5410.711753544724</v>
+        <v>5293.42291756918</v>
       </c>
       <c r="K91" t="n">
-        <v>4.412718370940309</v>
+        <v>4.459532457984951</v>
       </c>
     </row>
     <row r="92">
@@ -3826,25 +3826,25 @@
         <v>207</v>
       </c>
       <c r="E92" t="n">
-        <v>0.1899651345352254</v>
+        <v>0.19341272527449</v>
       </c>
       <c r="F92" t="n">
-        <v>0.1698150135037633</v>
+        <v>0.1733483652066912</v>
       </c>
       <c r="G92" t="n">
-        <v>9.427493474536309</v>
+        <v>9.639615946929583</v>
       </c>
       <c r="H92" t="n">
         <v>0.001</v>
       </c>
       <c r="I92" t="n">
-        <v>1060.365810237207</v>
+        <v>1040.384165363156</v>
       </c>
       <c r="J92" t="n">
-        <v>5581.896977208637</v>
+        <v>5379.088495271708</v>
       </c>
       <c r="K92" t="n">
-        <v>4.482980887075862</v>
+        <v>4.439575338383418</v>
       </c>
     </row>
     <row r="93">
@@ -3863,25 +3863,25 @@
         <v>212</v>
       </c>
       <c r="E93" t="n">
-        <v>0.194454201751158</v>
+        <v>0.1954239880917322</v>
       </c>
       <c r="F93" t="n">
-        <v>0.17490211926939</v>
+        <v>0.1758954441133761</v>
       </c>
       <c r="G93" t="n">
-        <v>9.945447086390073</v>
+        <v>10.00709465633104</v>
       </c>
       <c r="H93" t="n">
         <v>0.001</v>
       </c>
       <c r="I93" t="n">
-        <v>1109.347921704103</v>
+        <v>1087.619663043725</v>
       </c>
       <c r="J93" t="n">
-        <v>5704.931607102682</v>
+        <v>5565.435818110494</v>
       </c>
       <c r="K93" t="n">
-        <v>4.604197772217451</v>
+        <v>4.551947875484112</v>
       </c>
     </row>
     <row r="94">
@@ -3900,25 +3900,25 @@
         <v>216</v>
       </c>
       <c r="E94" t="n">
-        <v>0.1870785774179001</v>
+        <v>0.1904827117315498</v>
       </c>
       <c r="F94" t="n">
-        <v>0.1677233054516597</v>
+        <v>0.171208490582301</v>
       </c>
       <c r="G94" t="n">
-        <v>9.6655101382302</v>
+        <v>9.882770891573673</v>
       </c>
       <c r="H94" t="n">
         <v>0.001</v>
       </c>
       <c r="I94" t="n">
-        <v>1075.32820513473</v>
+        <v>1084.589043483569</v>
       </c>
       <c r="J94" t="n">
-        <v>5748.002897908714</v>
+        <v>5693.897538649579</v>
       </c>
       <c r="K94" t="n">
-        <v>4.388162878357402</v>
+        <v>4.471647866738395</v>
       </c>
     </row>
     <row r="95">
@@ -3937,25 +3937,25 @@
         <v>221</v>
       </c>
       <c r="E95" t="n">
-        <v>0.1874142986462784</v>
+        <v>0.1884090460244263</v>
       </c>
       <c r="F95" t="n">
-        <v>0.1685169567543313</v>
+        <v>0.1695348377924362</v>
       </c>
       <c r="G95" t="n">
-        <v>9.917495260333087</v>
+        <v>9.982354952781003</v>
       </c>
       <c r="H95" t="n">
         <v>0.001</v>
       </c>
       <c r="I95" t="n">
-        <v>1099.062136496782</v>
+        <v>1091.249558821619</v>
       </c>
       <c r="J95" t="n">
-        <v>5864.345167020192</v>
+        <v>5791.917011671213</v>
       </c>
       <c r="K95" t="n">
-        <v>4.402013526601426</v>
+        <v>4.394807317206665</v>
       </c>
     </row>
     <row r="96">
@@ -3974,25 +3974,25 @@
         <v>226</v>
       </c>
       <c r="E96" t="n">
-        <v>0.1854214466450859</v>
+        <v>0.1823331736476731</v>
       </c>
       <c r="F96" t="n">
-        <v>0.1669082977052015</v>
+        <v>0.1637498366851202</v>
       </c>
       <c r="G96" t="n">
-        <v>10.01566223267491</v>
+        <v>9.811648683715475</v>
       </c>
       <c r="H96" t="n">
         <v>0.001</v>
       </c>
       <c r="I96" t="n">
-        <v>1103.682521513989</v>
+        <v>1076.084361206928</v>
       </c>
       <c r="J96" t="n">
-        <v>5952.291611803357</v>
+        <v>5901.747551908862</v>
       </c>
       <c r="K96" t="n">
-        <v>4.298214931583275</v>
+        <v>4.195228694614494</v>
       </c>
     </row>
     <row r="97">
@@ -4011,25 +4011,25 @@
         <v>233</v>
       </c>
       <c r="E97" t="n">
-        <v>0.1856235176696469</v>
+        <v>0.1856235176696466</v>
       </c>
       <c r="F97" t="n">
-        <v>0.1676857096888021</v>
+        <v>0.1676857096888018</v>
       </c>
       <c r="G97" t="n">
-        <v>10.3481717424932</v>
+        <v>10.34817174249318</v>
       </c>
       <c r="H97" t="n">
         <v>0.001</v>
       </c>
       <c r="I97" t="n">
-        <v>1136.107764509159</v>
+        <v>1136.107764509158</v>
       </c>
       <c r="J97" t="n">
         <v>6120.49474534301</v>
       </c>
       <c r="K97" t="n">
-        <v>4.309345336910141</v>
+        <v>4.309345336910132</v>
       </c>
     </row>
   </sheetData>
